--- a/food_access_county.xlsx
+++ b/food_access_county.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="296">
   <si>
     <t>county</t>
   </si>
@@ -85,6 +85,33 @@
     <t>gap_score</t>
   </si>
   <si>
+    <t>county_fips</t>
+  </si>
+  <si>
+    <t>food_insecurity_rate</t>
+  </si>
+  <si>
+    <t>food_insecure_population</t>
+  </si>
+  <si>
+    <t>food_env_index</t>
+  </si>
+  <si>
+    <t>PovertyRate</t>
+  </si>
+  <si>
+    <t>MedianFamilyIncome</t>
+  </si>
+  <si>
+    <t>LILATracts_1And10</t>
+  </si>
+  <si>
+    <t>food_insecurity_pct</t>
+  </si>
+  <si>
+    <t>gap_score_enriched</t>
+  </si>
+  <si>
     <t>McCulloch</t>
   </si>
   <si>
@@ -127,45 +154,45 @@
     <t>Starr</t>
   </si>
   <si>
+    <t>Zavala</t>
+  </si>
+  <si>
+    <t>Jim Hogg</t>
+  </si>
+  <si>
+    <t>Bexar</t>
+  </si>
+  <si>
     <t>Sutton</t>
   </si>
   <si>
+    <t>Atascosa</t>
+  </si>
+  <si>
+    <t>Aransas</t>
+  </si>
+  <si>
+    <t>Lavaca</t>
+  </si>
+  <si>
+    <t>Sterling</t>
+  </si>
+  <si>
+    <t>Webb</t>
+  </si>
+  <si>
+    <t>Crockett</t>
+  </si>
+  <si>
+    <t>Concho</t>
+  </si>
+  <si>
     <t>Burnet</t>
   </si>
   <si>
-    <t>Bexar</t>
-  </si>
-  <si>
-    <t>Atascosa</t>
-  </si>
-  <si>
-    <t>Aransas</t>
-  </si>
-  <si>
-    <t>Zavala</t>
-  </si>
-  <si>
-    <t>Lavaca</t>
-  </si>
-  <si>
-    <t>Sterling</t>
-  </si>
-  <si>
-    <t>Webb</t>
-  </si>
-  <si>
-    <t>Crockett</t>
-  </si>
-  <si>
-    <t>Concho</t>
-  </si>
-  <si>
     <t>Colorado</t>
   </si>
   <si>
-    <t>Jim Hogg</t>
-  </si>
-  <si>
     <t>Menard</t>
   </si>
   <si>
@@ -205,30 +232,30 @@
     <t>Hays</t>
   </si>
   <si>
+    <t>Zapata</t>
+  </si>
+  <si>
+    <t>Dimmit</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
     <t>Bandera</t>
   </si>
   <si>
-    <t>Wilson</t>
+    <t>Hidalgo</t>
   </si>
   <si>
     <t>Val Verde</t>
   </si>
   <si>
-    <t>Hidalgo</t>
-  </si>
-  <si>
     <t>Gillespie</t>
   </si>
   <si>
-    <t>Dimmit</t>
-  </si>
-  <si>
     <t>Nueces</t>
   </si>
   <si>
-    <t>Zapata</t>
-  </si>
-  <si>
     <t>Medina</t>
   </si>
   <si>
@@ -307,21 +334,6 @@
     <t>Uvalde</t>
   </si>
   <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
     <t>West TX</t>
   </si>
   <si>
@@ -335,6 +347,561 @@
   </si>
   <si>
     <t>Gulf Coast</t>
+  </si>
+  <si>
+    <t>48307</t>
+  </si>
+  <si>
+    <t>48333</t>
+  </si>
+  <si>
+    <t>48137</t>
+  </si>
+  <si>
+    <t>48261</t>
+  </si>
+  <si>
+    <t>48383</t>
+  </si>
+  <si>
+    <t>48311</t>
+  </si>
+  <si>
+    <t>48081</t>
+  </si>
+  <si>
+    <t>48489</t>
+  </si>
+  <si>
+    <t>48047</t>
+  </si>
+  <si>
+    <t>48385</t>
+  </si>
+  <si>
+    <t>48297</t>
+  </si>
+  <si>
+    <t>48323</t>
+  </si>
+  <si>
+    <t>48283</t>
+  </si>
+  <si>
+    <t>48427</t>
+  </si>
+  <si>
+    <t>48507</t>
+  </si>
+  <si>
+    <t>48247</t>
+  </si>
+  <si>
+    <t>48029</t>
+  </si>
+  <si>
+    <t>48435</t>
+  </si>
+  <si>
+    <t>48013</t>
+  </si>
+  <si>
+    <t>48007</t>
+  </si>
+  <si>
+    <t>48285</t>
+  </si>
+  <si>
+    <t>48431</t>
+  </si>
+  <si>
+    <t>48479</t>
+  </si>
+  <si>
+    <t>48105</t>
+  </si>
+  <si>
+    <t>48095</t>
+  </si>
+  <si>
+    <t>48053</t>
+  </si>
+  <si>
+    <t>48089</t>
+  </si>
+  <si>
+    <t>48327</t>
+  </si>
+  <si>
+    <t>48461</t>
+  </si>
+  <si>
+    <t>48249</t>
+  </si>
+  <si>
+    <t>48235</t>
+  </si>
+  <si>
+    <t>48321</t>
+  </si>
+  <si>
+    <t>48319</t>
+  </si>
+  <si>
+    <t>48057</t>
+  </si>
+  <si>
+    <t>48175</t>
+  </si>
+  <si>
+    <t>48177</t>
+  </si>
+  <si>
+    <t>48271</t>
+  </si>
+  <si>
+    <t>48061</t>
+  </si>
+  <si>
+    <t>48131</t>
+  </si>
+  <si>
+    <t>48209</t>
+  </si>
+  <si>
+    <t>48505</t>
+  </si>
+  <si>
+    <t>48127</t>
+  </si>
+  <si>
+    <t>48493</t>
+  </si>
+  <si>
+    <t>48019</t>
+  </si>
+  <si>
+    <t>48215</t>
+  </si>
+  <si>
+    <t>48465</t>
+  </si>
+  <si>
+    <t>48171</t>
+  </si>
+  <si>
+    <t>48355</t>
+  </si>
+  <si>
+    <t>48325</t>
+  </si>
+  <si>
+    <t>48391</t>
+  </si>
+  <si>
+    <t>48239</t>
+  </si>
+  <si>
+    <t>48413</t>
+  </si>
+  <si>
+    <t>48267</t>
+  </si>
+  <si>
+    <t>48025</t>
+  </si>
+  <si>
+    <t>48149</t>
+  </si>
+  <si>
+    <t>48451</t>
+  </si>
+  <si>
+    <t>48469</t>
+  </si>
+  <si>
+    <t>48123</t>
+  </si>
+  <si>
+    <t>48255</t>
+  </si>
+  <si>
+    <t>48281</t>
+  </si>
+  <si>
+    <t>48163</t>
+  </si>
+  <si>
+    <t>48411</t>
+  </si>
+  <si>
+    <t>48265</t>
+  </si>
+  <si>
+    <t>48055</t>
+  </si>
+  <si>
+    <t>48021</t>
+  </si>
+  <si>
+    <t>48031</t>
+  </si>
+  <si>
+    <t>48273</t>
+  </si>
+  <si>
+    <t>48259</t>
+  </si>
+  <si>
+    <t>48187</t>
+  </si>
+  <si>
+    <t>48091</t>
+  </si>
+  <si>
+    <t>48409</t>
+  </si>
+  <si>
+    <t>48299</t>
+  </si>
+  <si>
+    <t>48453</t>
+  </si>
+  <si>
+    <t>48463</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>3960</t>
+  </si>
+  <si>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>1820</t>
+  </si>
+  <si>
+    <t>11270</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>15550</t>
+  </si>
+  <si>
+    <t>2140</t>
+  </si>
+  <si>
+    <t>980</t>
+  </si>
+  <si>
+    <t>278860</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>5740</t>
+  </si>
+  <si>
+    <t>4320</t>
+  </si>
+  <si>
+    <t>2460</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>42720</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>5560</t>
+  </si>
+  <si>
+    <t>2050</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>7010</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>6320</t>
+  </si>
+  <si>
+    <t>2520</t>
+  </si>
+  <si>
+    <t>970</t>
+  </si>
+  <si>
+    <t>2620</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>75650</t>
+  </si>
+  <si>
+    <t>1850</t>
+  </si>
+  <si>
+    <t>27620</t>
+  </si>
+  <si>
+    <t>3190</t>
+  </si>
+  <si>
+    <t>2240</t>
+  </si>
+  <si>
+    <t>5240</t>
+  </si>
+  <si>
+    <t>2800</t>
+  </si>
+  <si>
+    <t>164390</t>
+  </si>
+  <si>
+    <t>7050</t>
+  </si>
+  <si>
+    <t>3410</t>
+  </si>
+  <si>
+    <t>54330</t>
+  </si>
+  <si>
+    <t>6490</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>5090</t>
+  </si>
+  <si>
+    <t>2860</t>
+  </si>
+  <si>
+    <t>15290</t>
+  </si>
+  <si>
+    <t>13700</t>
+  </si>
+  <si>
+    <t>2890</t>
+  </si>
+  <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>2930</t>
+  </si>
+  <si>
+    <t>790</t>
+  </si>
+  <si>
+    <t>7210</t>
+  </si>
+  <si>
+    <t>5940</t>
+  </si>
+  <si>
+    <t>10710</t>
+  </si>
+  <si>
+    <t>1430</t>
+  </si>
+  <si>
+    <t>5770</t>
+  </si>
+  <si>
+    <t>4250</t>
+  </si>
+  <si>
+    <t>18160</t>
+  </si>
+  <si>
+    <t>17670</t>
+  </si>
+  <si>
+    <t>11380</t>
+  </si>
+  <si>
+    <t>2970</t>
+  </si>
+  <si>
+    <t>150980</t>
+  </si>
+  <si>
+    <t>3970</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>8.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>6.6</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>4.9</t>
   </si>
 </sst>
 </file>
@@ -692,10 +1259,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:AF75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,10 +1332,37 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>1058</v>
@@ -803,11 +1397,11 @@
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>97</v>
+      <c r="Q2">
+        <v>9</v>
       </c>
       <c r="R2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U2" t="b">
         <v>1</v>
@@ -818,10 +1412,37 @@
       <c r="W2">
         <v>10</v>
       </c>
+      <c r="X2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y2">
+        <v>0.169</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB2">
+        <v>13.64931309272283</v>
+      </c>
+      <c r="AC2">
+        <v>56149.66666666666</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>16.9</v>
+      </c>
+      <c r="AF2">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>354</v>
@@ -856,11 +1477,11 @@
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>98</v>
+      <c r="Q3">
+        <v>7</v>
       </c>
       <c r="R3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="U3" t="b">
         <v>1</v>
@@ -871,10 +1492,37 @@
       <c r="W3">
         <v>10</v>
       </c>
+      <c r="X3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3">
+        <v>0.121</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB3">
+        <v>16.25591481867045</v>
+      </c>
+      <c r="AC3">
+        <v>55275</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>12.1</v>
+      </c>
+      <c r="AF3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>240</v>
@@ -909,11 +1557,11 @@
       <c r="L4">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>99</v>
+      <c r="Q4">
+        <v>8</v>
       </c>
       <c r="R4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -924,10 +1572,37 @@
       <c r="W4">
         <v>8</v>
       </c>
+      <c r="X4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y4">
+        <v>0.14</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB4">
+        <v>6.656877141458641</v>
+      </c>
+      <c r="AC4">
+        <v>56688</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>14</v>
+      </c>
+      <c r="AF4">
+        <v>8</v>
+      </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>24</v>
@@ -962,11 +1637,11 @@
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="Q5" t="s">
-        <v>100</v>
+      <c r="Q5">
+        <v>11</v>
       </c>
       <c r="R5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="U5" t="b">
         <v>1</v>
@@ -977,10 +1652,37 @@
       <c r="W5">
         <v>8</v>
       </c>
+      <c r="X5" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y5">
+        <v>0.128</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB5">
+        <v>7.05882352941176</v>
+      </c>
+      <c r="AC5">
+        <v>40625</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>12.8</v>
+      </c>
+      <c r="AF5">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>272</v>
@@ -1015,11 +1717,11 @@
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="Q6" t="s">
-        <v>97</v>
+      <c r="Q6">
+        <v>9</v>
       </c>
       <c r="R6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U6" t="b">
         <v>1</v>
@@ -1030,10 +1732,37 @@
       <c r="W6">
         <v>8</v>
       </c>
+      <c r="X6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y6">
+        <v>0.107</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB6">
+        <v>14.7739504843918</v>
+      </c>
+      <c r="AC6">
+        <v>74432</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>10.7</v>
+      </c>
+      <c r="AF6">
+        <v>8</v>
+      </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>73</v>
@@ -1068,11 +1797,11 @@
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="Q7" t="s">
-        <v>100</v>
+      <c r="Q7">
+        <v>11</v>
       </c>
       <c r="R7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="U7" t="b">
         <v>1</v>
@@ -1083,10 +1812,37 @@
       <c r="W7">
         <v>8</v>
       </c>
+      <c r="X7" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y7">
+        <v>0.099</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB7">
+        <v>12.8398791540786</v>
+      </c>
+      <c r="AC7">
+        <v>72750</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>9.9</v>
+      </c>
+      <c r="AF7">
+        <v>8</v>
+      </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>257</v>
@@ -1121,11 +1877,11 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="Q8" t="s">
-        <v>97</v>
+      <c r="Q8">
+        <v>9</v>
       </c>
       <c r="R8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U8" t="b">
         <v>1</v>
@@ -1136,10 +1892,37 @@
       <c r="W8">
         <v>8</v>
       </c>
+      <c r="X8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y8">
+        <v>0.152</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB8">
+        <v>15.6636904594446</v>
+      </c>
+      <c r="AC8">
+        <v>59228.5</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>15.2</v>
+      </c>
+      <c r="AF8">
+        <v>8</v>
+      </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>4124</v>
@@ -1186,11 +1969,11 @@
       <c r="P9">
         <v>0.5</v>
       </c>
-      <c r="Q9" t="s">
-        <v>100</v>
+      <c r="Q9">
+        <v>11</v>
       </c>
       <c r="R9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S9">
         <v>2062</v>
@@ -1207,10 +1990,37 @@
       <c r="W9">
         <v>6</v>
       </c>
+      <c r="X9" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y9">
+        <v>0.194</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB9">
+        <v>30.6606068387877</v>
+      </c>
+      <c r="AC9">
+        <v>36683.6</v>
+      </c>
+      <c r="AD9">
+        <v>3</v>
+      </c>
+      <c r="AE9">
+        <v>19.4</v>
+      </c>
+      <c r="AF9">
+        <v>6</v>
+      </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>1954</v>
@@ -1257,11 +2067,11 @@
       <c r="P10">
         <v>5</v>
       </c>
-      <c r="Q10" t="s">
-        <v>100</v>
+      <c r="Q10">
+        <v>11</v>
       </c>
       <c r="R10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S10">
         <v>1954</v>
@@ -1278,10 +2088,37 @@
       <c r="W10">
         <v>5</v>
       </c>
+      <c r="X10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y10">
+        <v>0.233</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB10">
+        <v>37.12217510644845</v>
+      </c>
+      <c r="AC10">
+        <v>29893</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>23.3</v>
+      </c>
+      <c r="AF10">
+        <v>6</v>
+      </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>332</v>
@@ -1328,11 +2165,11 @@
       <c r="P11">
         <v>0</v>
       </c>
-      <c r="Q11" t="s">
-        <v>99</v>
+      <c r="Q11">
+        <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S11">
         <v>332</v>
@@ -1349,10 +2186,37 @@
       <c r="W11">
         <v>5</v>
       </c>
+      <c r="X11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y11">
+        <v>0.213</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB11">
+        <v>22.812879708384</v>
+      </c>
+      <c r="AC11">
+        <v>50000</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>21.3</v>
+      </c>
+      <c r="AF11">
+        <v>6</v>
+      </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>1229</v>
@@ -1399,11 +2263,11 @@
       <c r="P12">
         <v>3.5</v>
       </c>
-      <c r="Q12" t="s">
-        <v>100</v>
+      <c r="Q12">
+        <v>11</v>
       </c>
       <c r="R12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S12">
         <v>614</v>
@@ -1420,10 +2284,37 @@
       <c r="W12">
         <v>5</v>
       </c>
+      <c r="X12" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y12">
+        <v>0.16</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB12">
+        <v>15.7951107363978</v>
+      </c>
+      <c r="AC12">
+        <v>60481</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>16</v>
+      </c>
+      <c r="AF12">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>15337</v>
@@ -1470,11 +2361,11 @@
       <c r="P13">
         <v>2.5</v>
       </c>
-      <c r="Q13" t="s">
-        <v>99</v>
+      <c r="Q13">
+        <v>8</v>
       </c>
       <c r="R13" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S13">
         <v>3834</v>
@@ -1491,10 +2382,37 @@
       <c r="W13">
         <v>5</v>
       </c>
+      <c r="X13" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y13">
+        <v>0.195</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB13">
+        <v>26.65128595503306</v>
+      </c>
+      <c r="AC13">
+        <v>42852.77777777778</v>
+      </c>
+      <c r="AD13">
+        <v>5</v>
+      </c>
+      <c r="AE13">
+        <v>19.5</v>
+      </c>
+      <c r="AF13">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>1082</v>
@@ -1541,11 +2459,11 @@
       <c r="P14">
         <v>0</v>
       </c>
-      <c r="Q14" t="s">
-        <v>99</v>
+      <c r="Q14">
+        <v>8</v>
       </c>
       <c r="R14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S14">
         <v>1082</v>
@@ -1562,10 +2480,37 @@
       <c r="W14">
         <v>5</v>
       </c>
+      <c r="X14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y14">
+        <v>0.143</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB14">
+        <v>12.1464997681966</v>
+      </c>
+      <c r="AC14">
+        <v>53699</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>14.3</v>
+      </c>
+      <c r="AF14">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>17798</v>
@@ -1612,11 +2557,11 @@
       <c r="P15">
         <v>4</v>
       </c>
-      <c r="Q15" t="s">
-        <v>100</v>
+      <c r="Q15">
+        <v>11</v>
       </c>
       <c r="R15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S15">
         <v>3560</v>
@@ -1633,19 +2578,46 @@
       <c r="W15">
         <v>4</v>
       </c>
+      <c r="X15" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y15">
+        <v>0.237</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB15">
+        <v>35.09875408544925</v>
+      </c>
+      <c r="AC15">
+        <v>33653.73333333333</v>
+      </c>
+      <c r="AD15">
+        <v>8</v>
+      </c>
+      <c r="AE15">
+        <v>23.7</v>
+      </c>
+      <c r="AF15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B16">
-        <v>281</v>
+        <v>3033</v>
       </c>
       <c r="C16">
-        <v>132</v>
+        <v>1394</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1654,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1669,116 +2641,170 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O16">
+        <v>75</v>
+      </c>
+      <c r="P16">
+        <v>3.75</v>
+      </c>
+      <c r="Q16">
+        <v>8</v>
+      </c>
+      <c r="R16" t="s">
+        <v>108</v>
+      </c>
+      <c r="S16">
+        <v>758</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>3</v>
+      </c>
+      <c r="X16" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y16">
+        <v>0.216</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB16">
+        <v>39.47179649750809</v>
+      </c>
+      <c r="AC16">
+        <v>33457</v>
+      </c>
+      <c r="AD16">
+        <v>3</v>
+      </c>
+      <c r="AE16">
+        <v>21.6</v>
+      </c>
+      <c r="AF16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>1091</v>
+      </c>
+      <c r="C17">
+        <v>473</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
         <v>100</v>
       </c>
-      <c r="P16">
+      <c r="N17">
+        <v>33.3</v>
+      </c>
+      <c r="O17">
+        <v>33.3</v>
+      </c>
+      <c r="P17">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q17">
+        <v>11</v>
+      </c>
+      <c r="R17" t="s">
+        <v>109</v>
+      </c>
+      <c r="S17">
+        <v>364</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>3</v>
+      </c>
+      <c r="X17" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y17">
+        <v>0.202</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB17">
+        <v>27.229997055395</v>
+      </c>
+      <c r="AC17">
+        <v>43331</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>20.2</v>
+      </c>
+      <c r="AF17">
         <v>4</v>
       </c>
-      <c r="Q16" t="s">
-        <v>97</v>
-      </c>
-      <c r="R16" t="s">
-        <v>102</v>
-      </c>
-      <c r="S16">
-        <v>281</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="b">
-        <v>1</v>
-      </c>
-      <c r="W16">
-        <v>3</v>
-      </c>
     </row>
-    <row r="17" spans="1:23">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17">
-        <v>3260</v>
-      </c>
-      <c r="C17">
-        <v>1555</v>
-      </c>
-      <c r="D17">
-        <v>17</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>4</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>2</v>
-      </c>
-      <c r="L17">
-        <v>2</v>
-      </c>
-      <c r="M17">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="N17">
-        <v>58.8</v>
-      </c>
-      <c r="O17">
-        <v>47.1</v>
-      </c>
-      <c r="P17">
-        <v>1.235294117647059</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>98</v>
-      </c>
-      <c r="R17" t="s">
-        <v>103</v>
-      </c>
-      <c r="S17">
-        <v>192</v>
-      </c>
-      <c r="T17">
-        <v>11.8</v>
-      </c>
-      <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="V17" t="b">
-        <v>1</v>
-      </c>
-      <c r="W17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:32">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>259720</v>
@@ -1825,11 +2851,11 @@
       <c r="P18">
         <v>2.197674418604651</v>
       </c>
-      <c r="Q18" t="s">
-        <v>99</v>
+      <c r="Q18">
+        <v>8</v>
       </c>
       <c r="R18" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S18">
         <v>3020</v>
@@ -1846,25 +2872,52 @@
       <c r="W18">
         <v>3</v>
       </c>
+      <c r="X18" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y18">
+        <v>0.14</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB18">
+        <v>17.26007516464241</v>
+      </c>
+      <c r="AC18">
+        <v>68590.43093922651</v>
+      </c>
+      <c r="AD18">
+        <v>70</v>
+      </c>
+      <c r="AE18">
+        <v>14</v>
+      </c>
+      <c r="AF18">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:32">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B19">
-        <v>8424</v>
+        <v>281</v>
       </c>
       <c r="C19">
-        <v>3674</v>
+        <v>132</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1879,34 +2932,34 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>2.714285714285714</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>99</v>
+        <v>4</v>
+      </c>
+      <c r="Q19">
+        <v>9</v>
       </c>
       <c r="R19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S19">
-        <v>1203</v>
+        <v>281</v>
       </c>
       <c r="T19">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
@@ -1917,28 +2970,55 @@
       <c r="W19">
         <v>3</v>
       </c>
+      <c r="X19" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y19">
+        <v>0.135</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB19">
+        <v>8.32682799895915</v>
+      </c>
+      <c r="AC19">
+        <v>63849</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>13.5</v>
+      </c>
+      <c r="AF19">
+        <v>3</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:32">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B20">
-        <v>3117</v>
+        <v>8424</v>
       </c>
       <c r="C20">
-        <v>1655</v>
+        <v>3674</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1950,34 +3030,34 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>100</v>
+        <v>2.714285714285714</v>
+      </c>
+      <c r="Q20">
+        <v>8</v>
       </c>
       <c r="R20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="S20">
-        <v>1039</v>
+        <v>1203</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
@@ -1988,19 +3068,46 @@
       <c r="W20">
         <v>3</v>
       </c>
+      <c r="X20" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y20">
+        <v>0.118</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB20">
+        <v>15.55547228644085</v>
+      </c>
+      <c r="AC20">
+        <v>60860.625</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AE20">
+        <v>11.8</v>
+      </c>
+      <c r="AF20">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:32">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B21">
-        <v>3033</v>
+        <v>3117</v>
       </c>
       <c r="C21">
-        <v>1394</v>
+        <v>1655</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2009,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2024,28 +3131,28 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="O21">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>99</v>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>11</v>
       </c>
       <c r="R21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="S21">
-        <v>758</v>
+        <v>1039</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2059,10 +3166,37 @@
       <c r="W21">
         <v>3</v>
       </c>
+      <c r="X21" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y21">
+        <v>0.179</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB21">
+        <v>18.07949284602876</v>
+      </c>
+      <c r="AC21">
+        <v>66071.8</v>
+      </c>
+      <c r="AD21">
+        <v>2</v>
+      </c>
+      <c r="AE21">
+        <v>17.9</v>
+      </c>
+      <c r="AF21">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:32">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>1442</v>
@@ -2109,11 +3243,11 @@
       <c r="P22">
         <v>2</v>
       </c>
-      <c r="Q22" t="s">
-        <v>99</v>
+      <c r="Q22">
+        <v>8</v>
       </c>
       <c r="R22" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S22">
         <v>206</v>
@@ -2130,10 +3264,37 @@
       <c r="W22">
         <v>3</v>
       </c>
+      <c r="X22" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y22">
+        <v>0.121</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>272</v>
+      </c>
+      <c r="AB22">
+        <v>11.48220438684129</v>
+      </c>
+      <c r="AC22">
+        <v>68495.83333333333</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>12.1</v>
+      </c>
+      <c r="AF22">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:32">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>79</v>
@@ -2180,11 +3341,11 @@
       <c r="P23">
         <v>1.5</v>
       </c>
-      <c r="Q23" t="s">
-        <v>97</v>
+      <c r="Q23">
+        <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S23">
         <v>40</v>
@@ -2201,10 +3362,37 @@
       <c r="W23">
         <v>3</v>
       </c>
+      <c r="X23" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y23">
+        <v>0.082</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>273</v>
+      </c>
+      <c r="AB23">
+        <v>3.53581142339075</v>
+      </c>
+      <c r="AC23">
+        <v>68411</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AF23">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:32">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>60807</v>
@@ -2251,11 +3439,11 @@
       <c r="P24">
         <v>3.041666666666667</v>
       </c>
-      <c r="Q24" t="s">
-        <v>100</v>
+      <c r="Q24">
+        <v>11</v>
       </c>
       <c r="R24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S24">
         <v>2534</v>
@@ -2272,10 +3460,37 @@
       <c r="W24">
         <v>3</v>
       </c>
+      <c r="X24" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y24">
+        <v>0.16</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB24">
+        <v>33.55941432703644</v>
+      </c>
+      <c r="AC24">
+        <v>44291.05</v>
+      </c>
+      <c r="AD24">
+        <v>11</v>
+      </c>
+      <c r="AE24">
+        <v>16</v>
+      </c>
+      <c r="AF24">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:32">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>248</v>
@@ -2322,11 +3537,11 @@
       <c r="P25">
         <v>4</v>
       </c>
-      <c r="Q25" t="s">
-        <v>97</v>
+      <c r="Q25">
+        <v>9</v>
       </c>
       <c r="R25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S25">
         <v>83</v>
@@ -2343,10 +3558,37 @@
       <c r="W25">
         <v>3</v>
       </c>
+      <c r="X25" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y25">
+        <v>0.114</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB25">
+        <v>20.7642596234897</v>
+      </c>
+      <c r="AC25">
+        <v>68450</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>11.4</v>
+      </c>
+      <c r="AF25">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:32">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>249</v>
@@ -2393,11 +3635,11 @@
       <c r="P26">
         <v>5</v>
       </c>
-      <c r="Q26" t="s">
-        <v>97</v>
+      <c r="Q26">
+        <v>9</v>
       </c>
       <c r="R26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S26">
         <v>249</v>
@@ -2414,152 +3656,233 @@
       <c r="W26">
         <v>3</v>
       </c>
+      <c r="X26" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y26">
+        <v>0.135</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB26">
+        <v>7.268578878748371</v>
+      </c>
+      <c r="AC26">
+        <v>57875</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>13.5</v>
+      </c>
+      <c r="AF26">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:32">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B27">
+        <v>3260</v>
+      </c>
+      <c r="C27">
+        <v>1555</v>
+      </c>
+      <c r="D27">
+        <v>17</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="N27">
+        <v>58.8</v>
+      </c>
+      <c r="O27">
+        <v>47.1</v>
+      </c>
+      <c r="P27">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="Q27">
+        <v>7</v>
+      </c>
+      <c r="R27" t="s">
+        <v>107</v>
+      </c>
+      <c r="S27">
+        <v>192</v>
+      </c>
+      <c r="T27">
+        <v>11.8</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27">
+        <v>3</v>
+      </c>
+      <c r="X27" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y27">
+        <v>0.115</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB27">
+        <v>10.56717274351188</v>
+      </c>
+      <c r="AC27">
+        <v>71494.25</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>11.5</v>
+      </c>
+      <c r="AF27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28">
         <v>2200</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>1006</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>5</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>3</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>80</v>
       </c>
-      <c r="N27">
+      <c r="N28">
         <v>80</v>
       </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>101</v>
-      </c>
-      <c r="R27" t="s">
-        <v>106</v>
-      </c>
-      <c r="S27">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>6</v>
+      </c>
+      <c r="R28" t="s">
+        <v>110</v>
+      </c>
+      <c r="S28">
         <v>440</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27" t="b">
-        <v>0</v>
-      </c>
-      <c r="V27" t="b">
-        <v>1</v>
-      </c>
-      <c r="W27">
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>3</v>
+      </c>
+      <c r="X28" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y28">
+        <v>0.1</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB28">
+        <v>10.98200315956885</v>
+      </c>
+      <c r="AC28">
+        <v>57728.4</v>
+      </c>
+      <c r="AD28">
+        <v>2</v>
+      </c>
+      <c r="AE28">
+        <v>10</v>
+      </c>
+      <c r="AF28">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
-      <c r="A28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28">
-        <v>1091</v>
-      </c>
-      <c r="C28">
-        <v>473</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
-      <c r="N28">
-        <v>33.3</v>
-      </c>
-      <c r="O28">
-        <v>33.3</v>
-      </c>
-      <c r="P28">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>100</v>
-      </c>
-      <c r="R28" t="s">
-        <v>105</v>
-      </c>
-      <c r="S28">
-        <v>364</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28" t="b">
-        <v>0</v>
-      </c>
-      <c r="V28" t="b">
-        <v>1</v>
-      </c>
-      <c r="W28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:32">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B29">
         <v>184</v>
@@ -2606,11 +3929,11 @@
       <c r="P29">
         <v>0</v>
       </c>
-      <c r="Q29" t="s">
-        <v>97</v>
+      <c r="Q29">
+        <v>9</v>
       </c>
       <c r="R29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S29">
         <v>46</v>
@@ -2627,10 +3950,37 @@
       <c r="W29">
         <v>3</v>
       </c>
+      <c r="X29" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y29">
+        <v>0.182</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>277</v>
+      </c>
+      <c r="AB29">
+        <v>9.88428158148505</v>
+      </c>
+      <c r="AC29">
+        <v>56688</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>18.2</v>
+      </c>
+      <c r="AF29">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:32">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B30">
         <v>262</v>
@@ -2677,11 +4027,11 @@
       <c r="P30">
         <v>0</v>
       </c>
-      <c r="Q30" t="s">
-        <v>97</v>
+      <c r="Q30">
+        <v>9</v>
       </c>
       <c r="R30" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S30">
         <v>262</v>
@@ -2698,10 +4048,37 @@
       <c r="W30">
         <v>3</v>
       </c>
+      <c r="X30" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y30">
+        <v>0.126</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB30">
+        <v>16.6188482216708</v>
+      </c>
+      <c r="AC30">
+        <v>72028.5</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>12.6</v>
+      </c>
+      <c r="AF30">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:32">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B31">
         <v>8503</v>
@@ -2748,11 +4125,11 @@
       <c r="P31">
         <v>3.75</v>
       </c>
-      <c r="Q31" t="s">
-        <v>100</v>
+      <c r="Q31">
+        <v>11</v>
       </c>
       <c r="R31" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S31">
         <v>2126</v>
@@ -2769,10 +4146,37 @@
       <c r="W31">
         <v>3</v>
       </c>
+      <c r="X31" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y31">
+        <v>0.179</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB31">
+        <v>22.9785145516815</v>
+      </c>
+      <c r="AC31">
+        <v>52703.42857142857</v>
+      </c>
+      <c r="AD31">
+        <v>4</v>
+      </c>
+      <c r="AE31">
+        <v>17.9</v>
+      </c>
+      <c r="AF31">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:32">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B32">
         <v>95</v>
@@ -2819,11 +4223,11 @@
       <c r="P32">
         <v>0</v>
       </c>
-      <c r="Q32" t="s">
-        <v>97</v>
+      <c r="Q32">
+        <v>9</v>
       </c>
       <c r="R32" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S32">
         <v>95</v>
@@ -2840,10 +4244,37 @@
       <c r="W32">
         <v>3</v>
       </c>
+      <c r="X32" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y32">
+        <v>0.136</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB32">
+        <v>14.8293963254593</v>
+      </c>
+      <c r="AC32">
+        <v>76389</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>13.6</v>
+      </c>
+      <c r="AF32">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:32">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B33">
         <v>5068</v>
@@ -2890,11 +4321,11 @@
       <c r="P33">
         <v>1.375</v>
       </c>
-      <c r="Q33" t="s">
-        <v>101</v>
+      <c r="Q33">
+        <v>6</v>
       </c>
       <c r="R33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="S33">
         <v>634</v>
@@ -2911,10 +4342,37 @@
       <c r="W33">
         <v>3</v>
       </c>
+      <c r="X33" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y33">
+        <v>0.174</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>281</v>
+      </c>
+      <c r="AB33">
+        <v>20.36663306550204</v>
+      </c>
+      <c r="AC33">
+        <v>59117</v>
+      </c>
+      <c r="AD33">
+        <v>3</v>
+      </c>
+      <c r="AE33">
+        <v>17.4</v>
+      </c>
+      <c r="AF33">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:32">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B34">
         <v>264</v>
@@ -2961,11 +4419,11 @@
       <c r="P34">
         <v>0</v>
       </c>
-      <c r="Q34" t="s">
-        <v>97</v>
+      <c r="Q34">
+        <v>9</v>
       </c>
       <c r="R34" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S34">
         <v>264</v>
@@ -2982,10 +4440,37 @@
       <c r="W34">
         <v>3</v>
       </c>
+      <c r="X34" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y34">
+        <v>0.116</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB34">
+        <v>14.11904489235</v>
+      </c>
+      <c r="AC34">
+        <v>53646</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>11.6</v>
+      </c>
+      <c r="AF34">
+        <v>3</v>
+      </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:32">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B35">
         <v>2381</v>
@@ -3032,11 +4517,11 @@
       <c r="P35">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Q35" t="s">
-        <v>99</v>
+      <c r="Q35">
+        <v>8</v>
       </c>
       <c r="R35" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S35">
         <v>397</v>
@@ -3053,10 +4538,37 @@
       <c r="W35">
         <v>3</v>
       </c>
+      <c r="X35" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y35">
+        <v>0.124</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>216</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB35">
+        <v>14.23208825812715</v>
+      </c>
+      <c r="AC35">
+        <v>67065.8</v>
+      </c>
+      <c r="AD35">
+        <v>2</v>
+      </c>
+      <c r="AE35">
+        <v>12.4</v>
+      </c>
+      <c r="AF35">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:32">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B36">
         <v>628</v>
@@ -3103,11 +4615,11 @@
       <c r="P36">
         <v>0.5714285714285714</v>
       </c>
-      <c r="Q36" t="s">
-        <v>99</v>
+      <c r="Q36">
+        <v>8</v>
       </c>
       <c r="R36" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S36">
         <v>90</v>
@@ -3124,10 +4636,37 @@
       <c r="W36">
         <v>3</v>
       </c>
+      <c r="X36" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y36">
+        <v>0.136</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB36">
+        <v>17.1103809315335</v>
+      </c>
+      <c r="AC36">
+        <v>77930.5</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>13.6</v>
+      </c>
+      <c r="AF36">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:32">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B37">
         <v>2769</v>
@@ -3174,11 +4713,11 @@
       <c r="P37">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Q37" t="s">
-        <v>99</v>
+      <c r="Q37">
+        <v>8</v>
       </c>
       <c r="R37" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S37">
         <v>231</v>
@@ -3195,10 +4734,37 @@
       <c r="W37">
         <v>3</v>
       </c>
+      <c r="X37" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y37">
+        <v>0.133</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB37">
+        <v>15.51486597305606</v>
+      </c>
+      <c r="AC37">
+        <v>59487.16666666666</v>
+      </c>
+      <c r="AD37">
+        <v>1</v>
+      </c>
+      <c r="AE37">
+        <v>13.3</v>
+      </c>
+      <c r="AF37">
+        <v>3</v>
+      </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:32">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B38">
         <v>391</v>
@@ -3245,11 +4811,11 @@
       <c r="P38">
         <v>3.333333333333333</v>
       </c>
-      <c r="Q38" t="s">
-        <v>99</v>
+      <c r="Q38">
+        <v>8</v>
       </c>
       <c r="R38" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S38">
         <v>130</v>
@@ -3266,10 +4832,37 @@
       <c r="W38">
         <v>3</v>
       </c>
+      <c r="X38" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y38">
+        <v>0.193</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB38">
+        <v>18.620890311318</v>
+      </c>
+      <c r="AC38">
+        <v>54083</v>
+      </c>
+      <c r="AD38">
+        <v>1</v>
+      </c>
+      <c r="AE38">
+        <v>19.3</v>
+      </c>
+      <c r="AF38">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:32">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B39">
         <v>89015</v>
@@ -3316,11 +4909,11 @@
       <c r="P39">
         <v>2.904761904761905</v>
       </c>
-      <c r="Q39" t="s">
-        <v>100</v>
+      <c r="Q39">
+        <v>11</v>
       </c>
       <c r="R39" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S39">
         <v>4239</v>
@@ -3337,10 +4930,37 @@
       <c r="W39">
         <v>3</v>
       </c>
+      <c r="X39" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y39">
+        <v>0.18</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB39">
+        <v>32.93807267950098</v>
+      </c>
+      <c r="AC39">
+        <v>41031.57142857143</v>
+      </c>
+      <c r="AD39">
+        <v>31</v>
+      </c>
+      <c r="AE39">
+        <v>18</v>
+      </c>
+      <c r="AF39">
+        <v>3</v>
+      </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:32">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B40">
         <v>2561</v>
@@ -3387,11 +5007,11 @@
       <c r="P40">
         <v>2.5</v>
       </c>
-      <c r="Q40" t="s">
-        <v>100</v>
+      <c r="Q40">
+        <v>11</v>
       </c>
       <c r="R40" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S40">
         <v>1280</v>
@@ -3408,10 +5028,37 @@
       <c r="W40">
         <v>3</v>
       </c>
+      <c r="X40" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y40">
+        <v>0.185</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB40">
+        <v>24.1636296257439</v>
+      </c>
+      <c r="AC40">
+        <v>46913.66666666666</v>
+      </c>
+      <c r="AD40">
+        <v>1</v>
+      </c>
+      <c r="AE40">
+        <v>18.5</v>
+      </c>
+      <c r="AF40">
+        <v>3</v>
+      </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:32">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B41">
         <v>15277</v>
@@ -3458,11 +5105,11 @@
       <c r="P41">
         <v>3.142857142857143</v>
       </c>
-      <c r="Q41" t="s">
-        <v>98</v>
+      <c r="Q41">
+        <v>7</v>
       </c>
       <c r="R41" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S41">
         <v>2182</v>
@@ -3479,19 +5126,46 @@
       <c r="W41">
         <v>3</v>
       </c>
+      <c r="X41" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y41">
+        <v>0.118</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB41">
+        <v>17.91530339429697</v>
+      </c>
+      <c r="AC41">
+        <v>82822.45833333333</v>
+      </c>
+      <c r="AD41">
+        <v>1</v>
+      </c>
+      <c r="AE41">
+        <v>11.8</v>
+      </c>
+      <c r="AF41">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:32">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B42">
-        <v>1760</v>
+        <v>3582</v>
       </c>
       <c r="C42">
-        <v>901</v>
+        <v>1466</v>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3500,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -3512,341 +5186,476 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>100</v>
+      </c>
+      <c r="N42">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="O42">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="P42">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="Q42">
+        <v>11</v>
+      </c>
+      <c r="R42" t="s">
+        <v>109</v>
+      </c>
+      <c r="S42">
+        <v>276</v>
+      </c>
+      <c r="T42">
+        <v>69.2</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="W42">
+        <v>2</v>
+      </c>
+      <c r="X42" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y42">
+        <v>0.229</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB42">
+        <v>37.48260738597017</v>
+      </c>
+      <c r="AC42">
+        <v>34588.66666666666</v>
+      </c>
+      <c r="AD42">
+        <v>2</v>
+      </c>
+      <c r="AE42">
+        <v>22.9</v>
+      </c>
+      <c r="AF42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43">
+        <v>2208</v>
+      </c>
+      <c r="C43">
+        <v>972</v>
+      </c>
+      <c r="D43">
         <v>4</v>
       </c>
-      <c r="M42">
-        <v>91.7</v>
-      </c>
-      <c r="N42">
-        <v>83.3</v>
-      </c>
-      <c r="O42">
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>100</v>
+      </c>
+      <c r="N43">
         <v>50</v>
       </c>
-      <c r="P42">
-        <v>2.75</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>99</v>
-      </c>
-      <c r="R42" t="s">
-        <v>104</v>
-      </c>
-      <c r="S42">
-        <v>147</v>
-      </c>
-      <c r="T42">
-        <v>25</v>
-      </c>
-      <c r="U42" t="b">
-        <v>0</v>
-      </c>
-      <c r="V42" t="b">
-        <v>1</v>
-      </c>
-      <c r="W42">
-        <v>2</v>
+      <c r="O43">
+        <v>75</v>
+      </c>
+      <c r="P43">
+        <v>3.25</v>
+      </c>
+      <c r="Q43">
+        <v>8</v>
+      </c>
+      <c r="R43" t="s">
+        <v>108</v>
+      </c>
+      <c r="S43">
+        <v>552</v>
+      </c>
+      <c r="T43">
+        <v>50</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="W43">
+        <v>2</v>
+      </c>
+      <c r="X43" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y43">
+        <v>0.254</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB43">
+        <v>32.4042995528986</v>
+      </c>
+      <c r="AC43">
+        <v>34324</v>
+      </c>
+      <c r="AD43">
+        <v>2</v>
+      </c>
+      <c r="AE43">
+        <v>25.4</v>
+      </c>
+      <c r="AF43">
+        <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
-      <c r="A43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B43">
+    <row r="44" spans="1:32">
+      <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44">
         <v>3638</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>1659</v>
       </c>
-      <c r="D43">
+      <c r="D44">
         <v>9</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>3</v>
-      </c>
-      <c r="L43">
-        <v>2</v>
-      </c>
-      <c r="M43">
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>3</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44">
         <v>88.90000000000001</v>
-      </c>
-      <c r="N43">
-        <v>66.7</v>
-      </c>
-      <c r="O43">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="P43">
-        <v>2</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>99</v>
-      </c>
-      <c r="R43" t="s">
-        <v>104</v>
-      </c>
-      <c r="S43">
-        <v>404</v>
-      </c>
-      <c r="T43">
-        <v>33.3</v>
-      </c>
-      <c r="U43" t="b">
-        <v>0</v>
-      </c>
-      <c r="V43" t="b">
-        <v>1</v>
-      </c>
-      <c r="W43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
-      <c r="A44" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44">
-        <v>8956</v>
-      </c>
-      <c r="C44">
-        <v>3874</v>
-      </c>
-      <c r="D44">
-        <v>3</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <v>2</v>
-      </c>
-      <c r="L44">
-        <v>2</v>
-      </c>
-      <c r="M44">
-        <v>100</v>
       </c>
       <c r="N44">
         <v>66.7</v>
       </c>
       <c r="O44">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P44">
+        <v>2</v>
+      </c>
+      <c r="Q44">
+        <v>8</v>
+      </c>
+      <c r="R44" t="s">
+        <v>108</v>
+      </c>
+      <c r="S44">
+        <v>404</v>
+      </c>
+      <c r="T44">
+        <v>33.3</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="W44">
+        <v>2</v>
+      </c>
+      <c r="X44" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y44">
+        <v>0.106</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB44">
+        <v>11.15722653479144</v>
+      </c>
+      <c r="AC44">
+        <v>78805.45454545454</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>10.6</v>
+      </c>
+      <c r="AF44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32">
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45">
+        <v>1760</v>
+      </c>
+      <c r="C45">
+        <v>901</v>
+      </c>
+      <c r="D45">
+        <v>12</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>3</v>
+      </c>
+      <c r="L45">
         <v>4</v>
       </c>
-      <c r="Q44" t="s">
-        <v>99</v>
-      </c>
-      <c r="R44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S44">
-        <v>2985</v>
-      </c>
-      <c r="T44">
-        <v>66.7</v>
-      </c>
-      <c r="U44" t="b">
-        <v>0</v>
-      </c>
-      <c r="V44" t="b">
-        <v>0</v>
-      </c>
-      <c r="W44">
+      <c r="M45">
+        <v>91.7</v>
+      </c>
+      <c r="N45">
+        <v>83.3</v>
+      </c>
+      <c r="O45">
+        <v>50</v>
+      </c>
+      <c r="P45">
+        <v>2.75</v>
+      </c>
+      <c r="Q45">
+        <v>8</v>
+      </c>
+      <c r="R45" t="s">
+        <v>108</v>
+      </c>
+      <c r="S45">
+        <v>147</v>
+      </c>
+      <c r="T45">
+        <v>25</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+      <c r="X45" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y45">
+        <v>0.134</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB45">
+        <v>13.76209990809102</v>
+      </c>
+      <c r="AC45">
+        <v>64785.6</v>
+      </c>
+      <c r="AD45">
+        <v>1</v>
+      </c>
+      <c r="AE45">
+        <v>13.4</v>
+      </c>
+      <c r="AF45">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
-      <c r="A45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45">
+    <row r="46" spans="1:32">
+      <c r="A46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46">
         <v>192196</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>81809</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>28</v>
       </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45">
-        <v>3</v>
-      </c>
-      <c r="G45">
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
         <v>9</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <v>2</v>
-      </c>
-      <c r="K45">
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46">
         <v>5</v>
       </c>
-      <c r="L45">
+      <c r="L46">
         <v>12</v>
       </c>
-      <c r="M45">
+      <c r="M46">
         <v>85.7</v>
       </c>
-      <c r="N45">
+      <c r="N46">
         <v>46.4</v>
       </c>
-      <c r="O45">
+      <c r="O46">
         <v>60.7</v>
       </c>
-      <c r="P45">
+      <c r="P46">
         <v>2.714285714285714</v>
       </c>
-      <c r="Q45" t="s">
-        <v>100</v>
-      </c>
-      <c r="R45" t="s">
-        <v>105</v>
-      </c>
-      <c r="S45">
+      <c r="Q46">
+        <v>11</v>
+      </c>
+      <c r="R46" t="s">
+        <v>109</v>
+      </c>
+      <c r="S46">
         <v>6864</v>
       </c>
-      <c r="T45">
+      <c r="T46">
         <v>17.9</v>
       </c>
-      <c r="U45" t="b">
-        <v>0</v>
-      </c>
-      <c r="V45" t="b">
-        <v>0</v>
-      </c>
-      <c r="W45">
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>2</v>
+      </c>
+      <c r="X46" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y46">
+        <v>0.19</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB46">
+        <v>31.67733594969777</v>
+      </c>
+      <c r="AC46">
+        <v>42897.01801801802</v>
+      </c>
+      <c r="AD46">
+        <v>61</v>
+      </c>
+      <c r="AE46">
+        <v>19</v>
+      </c>
+      <c r="AF46">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
-      <c r="A46" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46">
-        <v>1003</v>
-      </c>
-      <c r="C46">
-        <v>472</v>
-      </c>
-      <c r="D46">
-        <v>9</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>2</v>
-      </c>
-      <c r="L46">
-        <v>5</v>
-      </c>
-      <c r="M46">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="N46">
-        <v>55.6</v>
-      </c>
-      <c r="O46">
-        <v>66.7</v>
-      </c>
-      <c r="P46">
-        <v>2.888888888888889</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>99</v>
-      </c>
-      <c r="R46" t="s">
-        <v>104</v>
-      </c>
-      <c r="S46">
-        <v>111</v>
-      </c>
-      <c r="T46">
-        <v>22.2</v>
-      </c>
-      <c r="U46" t="b">
-        <v>0</v>
-      </c>
-      <c r="V46" t="b">
-        <v>1</v>
-      </c>
-      <c r="W46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:32">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B47">
-        <v>2208</v>
+        <v>8956</v>
       </c>
       <c r="C47">
-        <v>972</v>
+        <v>3874</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3855,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -3864,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>2</v>
@@ -3876,181 +5685,262 @@
         <v>100</v>
       </c>
       <c r="N47">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O47">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>99</v>
+        <v>4</v>
+      </c>
+      <c r="Q47">
+        <v>8</v>
       </c>
       <c r="R47" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S47">
-        <v>552</v>
+        <v>2985</v>
       </c>
       <c r="T47">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="U47" t="b">
         <v>0</v>
       </c>
       <c r="V47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47">
         <v>2</v>
       </c>
+      <c r="X47" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y47">
+        <v>0.148</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB47">
+        <v>18.91913348477285</v>
+      </c>
+      <c r="AC47">
+        <v>51516</v>
+      </c>
+      <c r="AD47">
+        <v>4</v>
+      </c>
+      <c r="AE47">
+        <v>14.8</v>
+      </c>
+      <c r="AF47">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:32">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B48">
+        <v>1003</v>
+      </c>
+      <c r="C48">
+        <v>472</v>
+      </c>
+      <c r="D48">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+      <c r="L48">
+        <v>5</v>
+      </c>
+      <c r="M48">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N48">
+        <v>55.6</v>
+      </c>
+      <c r="O48">
+        <v>66.7</v>
+      </c>
+      <c r="P48">
+        <v>2.888888888888889</v>
+      </c>
+      <c r="Q48">
+        <v>8</v>
+      </c>
+      <c r="R48" t="s">
+        <v>108</v>
+      </c>
+      <c r="S48">
+        <v>111</v>
+      </c>
+      <c r="T48">
+        <v>22.2</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" t="b">
+        <v>1</v>
+      </c>
+      <c r="W48">
+        <v>2</v>
+      </c>
+      <c r="X48" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y48">
+        <v>0.127</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>229</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>272</v>
+      </c>
+      <c r="AB48">
+        <v>11.70126280863145</v>
+      </c>
+      <c r="AC48">
+        <v>69605.60000000001</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>12.7</v>
+      </c>
+      <c r="AF48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49">
         <v>54734</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>26879</v>
       </c>
-      <c r="D48">
+      <c r="D49">
         <v>26</v>
       </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48">
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
         <v>5</v>
       </c>
-      <c r="G48">
+      <c r="G49">
         <v>5</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>3</v>
-      </c>
-      <c r="J48">
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+      <c r="J49">
         <v>7</v>
       </c>
-      <c r="K48">
+      <c r="K49">
         <v>4</v>
       </c>
-      <c r="L48">
+      <c r="L49">
         <v>10</v>
       </c>
-      <c r="M48">
+      <c r="M49">
         <v>96.2</v>
       </c>
-      <c r="N48">
+      <c r="N49">
         <v>92.3</v>
       </c>
-      <c r="O48">
+      <c r="O49">
         <v>73.09999999999999</v>
       </c>
-      <c r="P48">
+      <c r="P49">
         <v>3.038461538461538</v>
       </c>
-      <c r="Q48" t="s">
-        <v>100</v>
-      </c>
-      <c r="R48" t="s">
-        <v>105</v>
-      </c>
-      <c r="S48">
+      <c r="Q49">
+        <v>11</v>
+      </c>
+      <c r="R49" t="s">
+        <v>109</v>
+      </c>
+      <c r="S49">
         <v>2105</v>
       </c>
-      <c r="T48">
+      <c r="T49">
         <v>15.4</v>
       </c>
-      <c r="U48" t="b">
-        <v>0</v>
-      </c>
-      <c r="V48" t="b">
-        <v>0</v>
-      </c>
-      <c r="W48">
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>2</v>
+      </c>
+      <c r="X49" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y49">
+        <v>0.154</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB49">
+        <v>16.04705776846765</v>
+      </c>
+      <c r="AC49">
+        <v>66308.06329113925</v>
+      </c>
+      <c r="AD49">
+        <v>16</v>
+      </c>
+      <c r="AE49">
+        <v>15.4</v>
+      </c>
+      <c r="AF49">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
-      <c r="A49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49">
-        <v>3582</v>
-      </c>
-      <c r="C49">
-        <v>1466</v>
-      </c>
-      <c r="D49">
-        <v>13</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>9</v>
-      </c>
-      <c r="L49">
-        <v>1</v>
-      </c>
-      <c r="M49">
-        <v>100</v>
-      </c>
-      <c r="N49">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="O49">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="P49">
-        <v>1.538461538461539</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>100</v>
-      </c>
-      <c r="R49" t="s">
-        <v>105</v>
-      </c>
-      <c r="S49">
-        <v>276</v>
-      </c>
-      <c r="T49">
-        <v>69.2</v>
-      </c>
-      <c r="U49" t="b">
-        <v>0</v>
-      </c>
-      <c r="V49" t="b">
-        <v>1</v>
-      </c>
-      <c r="W49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:32">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B50">
         <v>5785</v>
@@ -4097,11 +5987,11 @@
       <c r="P50">
         <v>2.5</v>
       </c>
-      <c r="Q50" t="s">
-        <v>99</v>
+      <c r="Q50">
+        <v>8</v>
       </c>
       <c r="R50" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S50">
         <v>723</v>
@@ -4118,10 +6008,37 @@
       <c r="W50">
         <v>2</v>
       </c>
+      <c r="X50" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y50">
+        <v>0.129</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB50">
+        <v>10.47677697204727</v>
+      </c>
+      <c r="AC50">
+        <v>72523</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>12.9</v>
+      </c>
+      <c r="AF50">
+        <v>2</v>
+      </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:32">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B51">
         <v>819</v>
@@ -4168,11 +6085,11 @@
       <c r="P51">
         <v>1.75</v>
       </c>
-      <c r="Q51" t="s">
-        <v>100</v>
+      <c r="Q51">
+        <v>11</v>
       </c>
       <c r="R51" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S51">
         <v>102</v>
@@ -4189,10 +6106,37 @@
       <c r="W51">
         <v>2</v>
       </c>
+      <c r="X51" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y51">
+        <v>0.159</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB51">
+        <v>18.39830418161595</v>
+      </c>
+      <c r="AC51">
+        <v>57083.5</v>
+      </c>
+      <c r="AD51">
+        <v>1</v>
+      </c>
+      <c r="AE51">
+        <v>15.9</v>
+      </c>
+      <c r="AF51">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:32">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B52">
         <v>1621</v>
@@ -4239,11 +6183,11 @@
       <c r="P52">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Q52" t="s">
-        <v>99</v>
+      <c r="Q52">
+        <v>8</v>
       </c>
       <c r="R52" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S52">
         <v>270</v>
@@ -4260,10 +6204,37 @@
       <c r="W52">
         <v>2</v>
       </c>
+      <c r="X52" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y52">
+        <v>0.134</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB52">
+        <v>13.75550486045714</v>
+      </c>
+      <c r="AC52">
+        <v>67676.66666666667</v>
+      </c>
+      <c r="AD52">
+        <v>1</v>
+      </c>
+      <c r="AE52">
+        <v>13.4</v>
+      </c>
+      <c r="AF52">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:32">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B53">
         <v>197</v>
@@ -4310,11 +6281,11 @@
       <c r="P53">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Q53" t="s">
-        <v>97</v>
+      <c r="Q53">
+        <v>9</v>
       </c>
       <c r="R53" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S53">
         <v>66</v>
@@ -4331,10 +6302,37 @@
       <c r="W53">
         <v>2</v>
       </c>
+      <c r="X53" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y53">
+        <v>0.107</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>290</v>
+      </c>
+      <c r="AB53">
+        <v>14.7664162038549</v>
+      </c>
+      <c r="AC53">
+        <v>66712</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>10.7</v>
+      </c>
+      <c r="AF53">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:32">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B54">
         <v>358</v>
@@ -4381,11 +6379,11 @@
       <c r="P54">
         <v>1.75</v>
       </c>
-      <c r="Q54" t="s">
-        <v>97</v>
+      <c r="Q54">
+        <v>9</v>
       </c>
       <c r="R54" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S54">
         <v>90</v>
@@ -4402,10 +6400,37 @@
       <c r="W54">
         <v>2</v>
       </c>
+      <c r="X54" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y54">
+        <v>0.142</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>291</v>
+      </c>
+      <c r="AB54">
+        <v>22.12147917629165</v>
+      </c>
+      <c r="AC54">
+        <v>52310.5</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>14.2</v>
+      </c>
+      <c r="AF54">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:32">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B55">
         <v>4311</v>
@@ -4452,11 +6477,11 @@
       <c r="P55">
         <v>1.666666666666667</v>
       </c>
-      <c r="Q55" t="s">
-        <v>100</v>
+      <c r="Q55">
+        <v>11</v>
       </c>
       <c r="R55" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S55">
         <v>718</v>
@@ -4473,10 +6498,37 @@
       <c r="W55">
         <v>1</v>
       </c>
+      <c r="X55" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y55">
+        <v>0.163</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>277</v>
+      </c>
+      <c r="AB55">
+        <v>18.42384950637563</v>
+      </c>
+      <c r="AC55">
+        <v>51307.85714285714</v>
+      </c>
+      <c r="AD55">
+        <v>3</v>
+      </c>
+      <c r="AE55">
+        <v>16.3</v>
+      </c>
+      <c r="AF55">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:32">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B56">
         <v>1475</v>
@@ -4523,11 +6575,11 @@
       <c r="P56">
         <v>1.166666666666667</v>
       </c>
-      <c r="Q56" t="s">
-        <v>98</v>
+      <c r="Q56">
+        <v>7</v>
       </c>
       <c r="R56" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S56">
         <v>246</v>
@@ -4544,10 +6596,37 @@
       <c r="W56">
         <v>1</v>
       </c>
+      <c r="X56" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y56">
+        <v>0.117</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>272</v>
+      </c>
+      <c r="AB56">
+        <v>9.86925565256</v>
+      </c>
+      <c r="AC56">
+        <v>70491.42857142857</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>11.7</v>
+      </c>
+      <c r="AF56">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:32">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B57">
         <v>11792</v>
@@ -4594,11 +6673,11 @@
       <c r="P57">
         <v>3.9375</v>
       </c>
-      <c r="Q57" t="s">
-        <v>97</v>
+      <c r="Q57">
+        <v>9</v>
       </c>
       <c r="R57" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S57">
         <v>737</v>
@@ -4615,10 +6694,37 @@
       <c r="W57">
         <v>1</v>
       </c>
+      <c r="X57" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y57">
+        <v>0.128</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB57">
+        <v>13.21785906579786</v>
+      </c>
+      <c r="AC57">
+        <v>62379.41666666666</v>
+      </c>
+      <c r="AD57">
+        <v>5</v>
+      </c>
+      <c r="AE57">
+        <v>12.8</v>
+      </c>
+      <c r="AF57">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:32">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B58">
         <v>13146</v>
@@ -4665,11 +6771,11 @@
       <c r="P58">
         <v>2.481481481481481</v>
       </c>
-      <c r="Q58" t="s">
-        <v>99</v>
+      <c r="Q58">
+        <v>8</v>
       </c>
       <c r="R58" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S58">
         <v>487</v>
@@ -4686,10 +6792,37 @@
       <c r="W58">
         <v>1</v>
       </c>
+      <c r="X58" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y58">
+        <v>0.15</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB58">
+        <v>16.67602213537759</v>
+      </c>
+      <c r="AC58">
+        <v>68015.59090909091</v>
+      </c>
+      <c r="AD58">
+        <v>4</v>
+      </c>
+      <c r="AE58">
+        <v>15</v>
+      </c>
+      <c r="AF58">
+        <v>1</v>
+      </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:32">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B59">
         <v>2619</v>
@@ -4736,11 +6869,11 @@
       <c r="P59">
         <v>0.1428571428571428</v>
       </c>
-      <c r="Q59" t="s">
-        <v>99</v>
+      <c r="Q59">
+        <v>8</v>
       </c>
       <c r="R59" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S59">
         <v>374</v>
@@ -4757,10 +6890,37 @@
       <c r="W59">
         <v>1</v>
       </c>
+      <c r="X59" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y59">
+        <v>0.146</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB59">
+        <v>15.50191938807774</v>
+      </c>
+      <c r="AC59">
+        <v>69291</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>14.6</v>
+      </c>
+      <c r="AF59">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:32">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B60">
         <v>1752</v>
@@ -4807,11 +6967,11 @@
       <c r="P60">
         <v>1</v>
       </c>
-      <c r="Q60" t="s">
-        <v>99</v>
+      <c r="Q60">
+        <v>8</v>
       </c>
       <c r="R60" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S60">
         <v>350</v>
@@ -4828,10 +6988,37 @@
       <c r="W60">
         <v>1</v>
       </c>
+      <c r="X60" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y60">
+        <v>0.137</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB60">
+        <v>17.25405555360545</v>
+      </c>
+      <c r="AC60">
+        <v>66714.75</v>
+      </c>
+      <c r="AD60">
+        <v>2</v>
+      </c>
+      <c r="AE60">
+        <v>13.7</v>
+      </c>
+      <c r="AF60">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:32">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B61">
         <v>2122</v>
@@ -4878,11 +7065,11 @@
       <c r="P61">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q61" t="s">
-        <v>98</v>
+      <c r="Q61">
+        <v>7</v>
       </c>
       <c r="R61" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S61">
         <v>707</v>
@@ -4899,10 +7086,37 @@
       <c r="W61">
         <v>1</v>
       </c>
+      <c r="X61" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y61">
+        <v>0.135</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB61">
+        <v>11.60297072174952</v>
+      </c>
+      <c r="AC61">
+        <v>70313.60000000001</v>
+      </c>
+      <c r="AD61">
+        <v>1</v>
+      </c>
+      <c r="AE61">
+        <v>13.5</v>
+      </c>
+      <c r="AF61">
+        <v>1</v>
+      </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:32">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B62">
         <v>3212</v>
@@ -4949,11 +7163,11 @@
       <c r="P62">
         <v>2.25</v>
       </c>
-      <c r="Q62" t="s">
-        <v>99</v>
+      <c r="Q62">
+        <v>8</v>
       </c>
       <c r="R62" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S62">
         <v>803</v>
@@ -4970,10 +7184,37 @@
       <c r="W62">
         <v>1</v>
       </c>
+      <c r="X62" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y62">
+        <v>0.159</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>277</v>
+      </c>
+      <c r="AB62">
+        <v>20.3029065312299</v>
+      </c>
+      <c r="AC62">
+        <v>45384.66666666666</v>
+      </c>
+      <c r="AD62">
+        <v>2</v>
+      </c>
+      <c r="AE62">
+        <v>15.9</v>
+      </c>
+      <c r="AF62">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:32">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B63">
         <v>476</v>
@@ -5020,11 +7261,11 @@
       <c r="P63">
         <v>0.7142857142857143</v>
       </c>
-      <c r="Q63" t="s">
-        <v>98</v>
+      <c r="Q63">
+        <v>7</v>
       </c>
       <c r="R63" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S63">
         <v>68</v>
@@ -5041,10 +7282,37 @@
       <c r="W63">
         <v>1</v>
       </c>
+      <c r="X63" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y63">
+        <v>0.137</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB63">
+        <v>15.5136485854571</v>
+      </c>
+      <c r="AC63">
+        <v>55777</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>13.7</v>
+      </c>
+      <c r="AF63">
+        <v>1</v>
+      </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:32">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B64">
         <v>3576</v>
@@ -5091,11 +7359,11 @@
       <c r="P64">
         <v>3.25</v>
       </c>
-      <c r="Q64" t="s">
-        <v>99</v>
+      <c r="Q64">
+        <v>8</v>
       </c>
       <c r="R64" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S64">
         <v>447</v>
@@ -5112,10 +7380,37 @@
       <c r="W64">
         <v>1</v>
       </c>
+      <c r="X64" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y64">
+        <v>0.138</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB64">
+        <v>12.3353452842773</v>
+      </c>
+      <c r="AC64">
+        <v>64100.8</v>
+      </c>
+      <c r="AD64">
+        <v>1</v>
+      </c>
+      <c r="AE64">
+        <v>13.8</v>
+      </c>
+      <c r="AF64">
+        <v>1</v>
+      </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B65">
         <v>6033</v>
@@ -5162,11 +7457,11 @@
       <c r="P65">
         <v>3.2</v>
       </c>
-      <c r="Q65" t="s">
-        <v>98</v>
+      <c r="Q65">
+        <v>7</v>
       </c>
       <c r="R65" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S65">
         <v>1207</v>
@@ -5183,10 +7478,37 @@
       <c r="W65">
         <v>0</v>
       </c>
+      <c r="X65" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y65">
+        <v>0.131</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB65">
+        <v>15.95373599151526</v>
+      </c>
+      <c r="AC65">
+        <v>62833.75</v>
+      </c>
+      <c r="AD65">
+        <v>4</v>
+      </c>
+      <c r="AE65">
+        <v>13.1</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B66">
         <v>10607</v>
@@ -5233,11 +7555,11 @@
       <c r="P66">
         <v>1.9</v>
       </c>
-      <c r="Q66" t="s">
-        <v>98</v>
+      <c r="Q66">
+        <v>7</v>
       </c>
       <c r="R66" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S66">
         <v>1061</v>
@@ -5254,10 +7576,37 @@
       <c r="W66">
         <v>0</v>
       </c>
+      <c r="X66" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y66">
+        <v>0.113</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB66">
+        <v>10.03821417973465</v>
+      </c>
+      <c r="AC66">
+        <v>73835.8</v>
+      </c>
+      <c r="AD66">
+        <v>3</v>
+      </c>
+      <c r="AE66">
+        <v>11.3</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:32">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B67">
         <v>563</v>
@@ -5304,11 +7653,11 @@
       <c r="P67">
         <v>1.666666666666667</v>
       </c>
-      <c r="Q67" t="s">
-        <v>98</v>
+      <c r="Q67">
+        <v>7</v>
       </c>
       <c r="R67" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S67">
         <v>94</v>
@@ -5325,10 +7674,37 @@
       <c r="W67">
         <v>0</v>
       </c>
+      <c r="X67" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y67">
+        <v>0.126</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB67">
+        <v>9.460431841561114</v>
+      </c>
+      <c r="AC67">
+        <v>66178</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>12.6</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B68">
         <v>5264</v>
@@ -5375,11 +7751,11 @@
       <c r="P68">
         <v>0.7333333333333333</v>
       </c>
-      <c r="Q68" t="s">
-        <v>100</v>
+      <c r="Q68">
+        <v>11</v>
       </c>
       <c r="R68" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S68">
         <v>351</v>
@@ -5396,10 +7772,37 @@
       <c r="W68">
         <v>0</v>
       </c>
+      <c r="X68" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y68">
+        <v>0.186</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>247</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB68">
+        <v>26.46976704214084</v>
+      </c>
+      <c r="AC68">
+        <v>53417.2</v>
+      </c>
+      <c r="AD68">
+        <v>3</v>
+      </c>
+      <c r="AE68">
+        <v>18.6</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B69">
         <v>1637</v>
@@ -5446,11 +7849,11 @@
       <c r="P69">
         <v>3</v>
       </c>
-      <c r="Q69" t="s">
-        <v>99</v>
+      <c r="Q69">
+        <v>8</v>
       </c>
       <c r="R69" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S69">
         <v>182</v>
@@ -5467,10 +7870,37 @@
       <c r="W69">
         <v>0</v>
       </c>
+      <c r="X69" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y69">
+        <v>0.097</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>294</v>
+      </c>
+      <c r="AB69">
+        <v>5.493250272424923</v>
+      </c>
+      <c r="AC69">
+        <v>98267</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:32">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B70">
         <v>13447</v>
@@ -5517,11 +7947,11 @@
       <c r="P70">
         <v>1.8</v>
       </c>
-      <c r="Q70" t="s">
-        <v>99</v>
+      <c r="Q70">
+        <v>8</v>
       </c>
       <c r="R70" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S70">
         <v>896</v>
@@ -5538,10 +7968,37 @@
       <c r="W70">
         <v>0</v>
       </c>
+      <c r="X70" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y70">
+        <v>0.107</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB70">
+        <v>9.767140251129691</v>
+      </c>
+      <c r="AC70">
+        <v>78914.31034482758</v>
+      </c>
+      <c r="AD70">
+        <v>3</v>
+      </c>
+      <c r="AE70">
+        <v>10.7</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B71">
         <v>8772</v>
@@ -5588,11 +8045,11 @@
       <c r="P71">
         <v>3.470588235294118</v>
       </c>
-      <c r="Q71" t="s">
-        <v>99</v>
+      <c r="Q71">
+        <v>8</v>
       </c>
       <c r="R71" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S71">
         <v>516</v>
@@ -5609,10 +8066,37 @@
       <c r="W71">
         <v>0</v>
       </c>
+      <c r="X71" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y71">
+        <v>0.113</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB71">
+        <v>8.876398510931251</v>
+      </c>
+      <c r="AC71">
+        <v>88117.75</v>
+      </c>
+      <c r="AD71">
+        <v>3</v>
+      </c>
+      <c r="AE71">
+        <v>11.3</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B72">
         <v>9663</v>
@@ -5659,11 +8143,11 @@
       <c r="P72">
         <v>1</v>
       </c>
-      <c r="Q72" t="s">
-        <v>100</v>
+      <c r="Q72">
+        <v>11</v>
       </c>
       <c r="R72" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S72">
         <v>1208</v>
@@ -5680,10 +8164,37 @@
       <c r="W72">
         <v>0</v>
       </c>
+      <c r="X72" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y72">
+        <v>0.166</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB72">
+        <v>15.52107361214972</v>
+      </c>
+      <c r="AC72">
+        <v>66464.9375</v>
+      </c>
+      <c r="AD72">
+        <v>3</v>
+      </c>
+      <c r="AE72">
+        <v>16.6</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:32">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B73">
         <v>1815</v>
@@ -5730,11 +8241,11 @@
       <c r="P73">
         <v>2.222222222222222</v>
       </c>
-      <c r="Q73" t="s">
-        <v>98</v>
+      <c r="Q73">
+        <v>7</v>
       </c>
       <c r="R73" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S73">
         <v>202</v>
@@ -5751,10 +8262,37 @@
       <c r="W73">
         <v>0</v>
       </c>
+      <c r="X73" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y73">
+        <v>0.14</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB73">
+        <v>10.8497073449848</v>
+      </c>
+      <c r="AC73">
+        <v>67344</v>
+      </c>
+      <c r="AD73">
+        <v>2</v>
+      </c>
+      <c r="AE73">
+        <v>14</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B74">
         <v>78899</v>
@@ -5801,11 +8339,11 @@
       <c r="P74">
         <v>2.533333333333333</v>
       </c>
-      <c r="Q74" t="s">
-        <v>98</v>
+      <c r="Q74">
+        <v>7</v>
       </c>
       <c r="R74" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S74">
         <v>1315</v>
@@ -5822,10 +8360,37 @@
       <c r="W74">
         <v>0</v>
       </c>
+      <c r="X74" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y74">
+        <v>0.119</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>272</v>
+      </c>
+      <c r="AB74">
+        <v>14.38464784497463</v>
+      </c>
+      <c r="AC74">
+        <v>97262.79146919432</v>
+      </c>
+      <c r="AD74">
+        <v>25</v>
+      </c>
+      <c r="AE74">
+        <v>11.9</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B75">
         <v>5238</v>
@@ -5872,11 +8437,11 @@
       <c r="P75">
         <v>1.142857142857143</v>
       </c>
-      <c r="Q75" t="s">
-        <v>99</v>
+      <c r="Q75">
+        <v>8</v>
       </c>
       <c r="R75" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S75">
         <v>748</v>
@@ -5891,6 +8456,33 @@
         <v>0</v>
       </c>
       <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y75">
+        <v>0.159</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>295</v>
+      </c>
+      <c r="AB75">
+        <v>16.02096740195723</v>
+      </c>
+      <c r="AC75">
+        <v>52440.2</v>
+      </c>
+      <c r="AD75">
+        <v>4</v>
+      </c>
+      <c r="AE75">
+        <v>15.9</v>
+      </c>
+      <c r="AF75">
         <v>0</v>
       </c>
     </row>

--- a/food_access_county.xlsx
+++ b/food_access_county.xlsx
@@ -133,6 +133,9 @@
     <t>Coke</t>
   </si>
   <si>
+    <t>Duval</t>
+  </si>
+  <si>
     <t>Willacy</t>
   </si>
   <si>
@@ -142,15 +145,15 @@
     <t>Real</t>
   </si>
   <si>
+    <t>La Salle</t>
+  </si>
+  <si>
     <t>Live Oak</t>
   </si>
   <si>
     <t>Maverick</t>
   </si>
   <si>
-    <t>La Salle</t>
-  </si>
-  <si>
     <t>Starr</t>
   </si>
   <si>
@@ -163,72 +166,69 @@
     <t>Bexar</t>
   </si>
   <si>
+    <t>Atascosa</t>
+  </si>
+  <si>
+    <t>Aransas</t>
+  </si>
+  <si>
+    <t>Lavaca</t>
+  </si>
+  <si>
+    <t>Sterling</t>
+  </si>
+  <si>
+    <t>Webb</t>
+  </si>
+  <si>
+    <t>Burnet</t>
+  </si>
+  <si>
+    <t>Crockett</t>
+  </si>
+  <si>
     <t>Sutton</t>
   </si>
   <si>
-    <t>Atascosa</t>
-  </si>
-  <si>
-    <t>Aransas</t>
-  </si>
-  <si>
-    <t>Lavaca</t>
-  </si>
-  <si>
-    <t>Sterling</t>
-  </si>
-  <si>
-    <t>Webb</t>
-  </si>
-  <si>
-    <t>Crockett</t>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Menard</t>
+  </si>
+  <si>
+    <t>Upton</t>
+  </si>
+  <si>
+    <t>Jim Wells</t>
+  </si>
+  <si>
+    <t>Irion</t>
+  </si>
+  <si>
+    <t>Matagorda</t>
+  </si>
+  <si>
+    <t>Mason</t>
+  </si>
+  <si>
+    <t>Calhoun</t>
+  </si>
+  <si>
+    <t>Goliad</t>
+  </si>
+  <si>
+    <t>Gonzales</t>
+  </si>
+  <si>
+    <t>Kinney</t>
+  </si>
+  <si>
+    <t>Cameron</t>
   </si>
   <si>
     <t>Concho</t>
   </si>
   <si>
-    <t>Burnet</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
-    <t>Menard</t>
-  </si>
-  <si>
-    <t>Upton</t>
-  </si>
-  <si>
-    <t>Jim Wells</t>
-  </si>
-  <si>
-    <t>Irion</t>
-  </si>
-  <si>
-    <t>Matagorda</t>
-  </si>
-  <si>
-    <t>Mason</t>
-  </si>
-  <si>
-    <t>Calhoun</t>
-  </si>
-  <si>
-    <t>Goliad</t>
-  </si>
-  <si>
-    <t>Gonzales</t>
-  </si>
-  <si>
-    <t>Kinney</t>
-  </si>
-  <si>
-    <t>Cameron</t>
-  </si>
-  <si>
-    <t>Duval</t>
-  </si>
-  <si>
     <t>Hays</t>
   </si>
   <si>
@@ -370,6 +370,9 @@
     <t>48081</t>
   </si>
   <si>
+    <t>48131</t>
+  </si>
+  <si>
     <t>48489</t>
   </si>
   <si>
@@ -379,15 +382,15 @@
     <t>48385</t>
   </si>
   <si>
+    <t>48283</t>
+  </si>
+  <si>
     <t>48297</t>
   </si>
   <si>
     <t>48323</t>
   </si>
   <si>
-    <t>48283</t>
-  </si>
-  <si>
     <t>48427</t>
   </si>
   <si>
@@ -400,72 +403,69 @@
     <t>48029</t>
   </si>
   <si>
+    <t>48013</t>
+  </si>
+  <si>
+    <t>48007</t>
+  </si>
+  <si>
+    <t>48285</t>
+  </si>
+  <si>
+    <t>48431</t>
+  </si>
+  <si>
+    <t>48479</t>
+  </si>
+  <si>
+    <t>48053</t>
+  </si>
+  <si>
+    <t>48105</t>
+  </si>
+  <si>
     <t>48435</t>
   </si>
   <si>
-    <t>48013</t>
-  </si>
-  <si>
-    <t>48007</t>
-  </si>
-  <si>
-    <t>48285</t>
-  </si>
-  <si>
-    <t>48431</t>
-  </si>
-  <si>
-    <t>48479</t>
-  </si>
-  <si>
-    <t>48105</t>
+    <t>48089</t>
+  </si>
+  <si>
+    <t>48327</t>
+  </si>
+  <si>
+    <t>48461</t>
+  </si>
+  <si>
+    <t>48249</t>
+  </si>
+  <si>
+    <t>48235</t>
+  </si>
+  <si>
+    <t>48321</t>
+  </si>
+  <si>
+    <t>48319</t>
+  </si>
+  <si>
+    <t>48057</t>
+  </si>
+  <si>
+    <t>48175</t>
+  </si>
+  <si>
+    <t>48177</t>
+  </si>
+  <si>
+    <t>48271</t>
+  </si>
+  <si>
+    <t>48061</t>
   </si>
   <si>
     <t>48095</t>
   </si>
   <si>
-    <t>48053</t>
-  </si>
-  <si>
-    <t>48089</t>
-  </si>
-  <si>
-    <t>48327</t>
-  </si>
-  <si>
-    <t>48461</t>
-  </si>
-  <si>
-    <t>48249</t>
-  </si>
-  <si>
-    <t>48235</t>
-  </si>
-  <si>
-    <t>48321</t>
-  </si>
-  <si>
-    <t>48319</t>
-  </si>
-  <si>
-    <t>48057</t>
-  </si>
-  <si>
-    <t>48175</t>
-  </si>
-  <si>
-    <t>48177</t>
-  </si>
-  <si>
-    <t>48271</t>
-  </si>
-  <si>
-    <t>48061</t>
-  </si>
-  <si>
-    <t>48131</t>
-  </si>
-  <si>
     <t>48209</t>
   </si>
   <si>
@@ -592,6 +592,9 @@
     <t>500</t>
   </si>
   <si>
+    <t>1850</t>
+  </si>
+  <si>
     <t>3960</t>
   </si>
   <si>
@@ -601,15 +604,15 @@
     <t>610</t>
   </si>
   <si>
+    <t>990</t>
+  </si>
+  <si>
     <t>1820</t>
   </si>
   <si>
     <t>11270</t>
   </si>
   <si>
-    <t>990</t>
-  </si>
-  <si>
     <t>15550</t>
   </si>
   <si>
@@ -622,66 +625,63 @@
     <t>278860</t>
   </si>
   <si>
+    <t>5740</t>
+  </si>
+  <si>
+    <t>4320</t>
+  </si>
+  <si>
+    <t>2460</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>42720</t>
+  </si>
+  <si>
+    <t>5560</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
     <t>460</t>
   </si>
   <si>
-    <t>5740</t>
-  </si>
-  <si>
-    <t>4320</t>
-  </si>
-  <si>
-    <t>2460</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>42720</t>
-  </si>
-  <si>
-    <t>340</t>
+    <t>2050</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>7010</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>6320</t>
+  </si>
+  <si>
+    <t>2520</t>
+  </si>
+  <si>
+    <t>970</t>
+  </si>
+  <si>
+    <t>2620</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>75650</t>
   </si>
   <si>
     <t>430</t>
   </si>
   <si>
-    <t>5560</t>
-  </si>
-  <si>
-    <t>2050</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>7010</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>6320</t>
-  </si>
-  <si>
-    <t>2520</t>
-  </si>
-  <si>
-    <t>970</t>
-  </si>
-  <si>
-    <t>2620</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>75650</t>
-  </si>
-  <si>
-    <t>1850</t>
-  </si>
-  <si>
     <t>27620</t>
   </si>
   <si>
@@ -802,6 +802,9 @@
     <t>3.9</t>
   </si>
   <si>
+    <t>5.5</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
@@ -811,12 +814,12 @@
     <t>1.3</t>
   </si>
   <si>
+    <t>6.6</t>
+  </si>
+  <si>
     <t>7.1</t>
   </si>
   <si>
-    <t>6.6</t>
-  </si>
-  <si>
     <t>3.3</t>
   </si>
   <si>
@@ -872,9 +875,6 @@
   </si>
   <si>
     <t>5.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
   </si>
   <si>
     <t>2.6</t>
@@ -1925,13 +1925,13 @@
         <v>39</v>
       </c>
       <c r="B9">
-        <v>4124</v>
+        <v>2561</v>
       </c>
       <c r="C9">
-        <v>1925</v>
+        <v>1271</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1964,10 +1964,10 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>11</v>
@@ -1976,10 +1976,10 @@
         <v>109</v>
       </c>
       <c r="S9">
-        <v>2062</v>
+        <v>2561</v>
       </c>
       <c r="T9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1988,13 +1988,13 @@
         <v>1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9" t="s">
         <v>118</v>
       </c>
       <c r="Y9">
-        <v>0.194</v>
+        <v>0.185</v>
       </c>
       <c r="Z9" t="s">
         <v>192</v>
@@ -2003,19 +2003,19 @@
         <v>262</v>
       </c>
       <c r="AB9">
-        <v>30.6606068387877</v>
+        <v>24.1636296257439</v>
       </c>
       <c r="AC9">
-        <v>36683.6</v>
+        <v>46913.66666666666</v>
       </c>
       <c r="AD9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE9">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:32">
@@ -2023,13 +2023,13 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>1954</v>
+        <v>4124</v>
       </c>
       <c r="C10">
-        <v>929</v>
+        <v>1925</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2050,22 +2050,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="Q10">
         <v>11</v>
@@ -2074,10 +2074,10 @@
         <v>109</v>
       </c>
       <c r="S10">
-        <v>1954</v>
+        <v>2062</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -2086,13 +2086,13 @@
         <v>1</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10" t="s">
         <v>119</v>
       </c>
       <c r="Y10">
-        <v>0.233</v>
+        <v>0.194</v>
       </c>
       <c r="Z10" t="s">
         <v>193</v>
@@ -2101,16 +2101,16 @@
         <v>263</v>
       </c>
       <c r="AB10">
-        <v>37.12217510644845</v>
+        <v>30.6606068387877</v>
       </c>
       <c r="AC10">
-        <v>29893</v>
+        <v>36683.6</v>
       </c>
       <c r="AD10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10">
-        <v>23.3</v>
+        <v>19.4</v>
       </c>
       <c r="AF10">
         <v>6</v>
@@ -2121,10 +2121,10 @@
         <v>41</v>
       </c>
       <c r="B11">
-        <v>332</v>
+        <v>1954</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>929</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2151,28 +2151,28 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S11">
-        <v>332</v>
+        <v>1954</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -2190,7 +2190,7 @@
         <v>120</v>
       </c>
       <c r="Y11">
-        <v>0.213</v>
+        <v>0.233</v>
       </c>
       <c r="Z11" t="s">
         <v>194</v>
@@ -2199,16 +2199,16 @@
         <v>264</v>
       </c>
       <c r="AB11">
-        <v>22.812879708384</v>
+        <v>37.12217510644845</v>
       </c>
       <c r="AC11">
-        <v>50000</v>
+        <v>29893</v>
       </c>
       <c r="AD11">
         <v>1</v>
       </c>
       <c r="AE11">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="AF11">
         <v>6</v>
@@ -2219,22 +2219,22 @@
         <v>42</v>
       </c>
       <c r="B12">
-        <v>1229</v>
+        <v>332</v>
       </c>
       <c r="C12">
-        <v>571</v>
+        <v>164</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2249,28 +2249,28 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S12">
-        <v>614</v>
+        <v>332</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         <v>121</v>
       </c>
       <c r="Y12">
-        <v>0.16</v>
+        <v>0.213</v>
       </c>
       <c r="Z12" t="s">
         <v>195</v>
@@ -2297,19 +2297,19 @@
         <v>265</v>
       </c>
       <c r="AB12">
-        <v>15.7951107363978</v>
+        <v>22.812879708384</v>
       </c>
       <c r="AC12">
-        <v>60481</v>
+        <v>50000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12">
-        <v>16</v>
+        <v>21.3</v>
       </c>
       <c r="AF12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -2317,13 +2317,13 @@
         <v>43</v>
       </c>
       <c r="B13">
-        <v>15337</v>
+        <v>1082</v>
       </c>
       <c r="C13">
-        <v>6621</v>
+        <v>506</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2347,19 +2347,19 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -2368,7 +2368,7 @@
         <v>108</v>
       </c>
       <c r="S13">
-        <v>3834</v>
+        <v>1082</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -2386,25 +2386,25 @@
         <v>122</v>
       </c>
       <c r="Y13">
-        <v>0.195</v>
+        <v>0.143</v>
       </c>
       <c r="Z13" t="s">
         <v>196</v>
       </c>
       <c r="AA13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AB13">
-        <v>26.65128595503306</v>
+        <v>12.1464997681966</v>
       </c>
       <c r="AC13">
-        <v>42852.77777777778</v>
+        <v>53699</v>
       </c>
       <c r="AD13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE13">
-        <v>19.5</v>
+        <v>14.3</v>
       </c>
       <c r="AF13">
         <v>5</v>
@@ -2415,22 +2415,22 @@
         <v>44</v>
       </c>
       <c r="B14">
-        <v>1082</v>
+        <v>1229</v>
       </c>
       <c r="C14">
-        <v>506</v>
+        <v>571</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2445,28 +2445,28 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S14">
-        <v>1082</v>
+        <v>1229</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2484,25 +2484,25 @@
         <v>123</v>
       </c>
       <c r="Y14">
-        <v>0.143</v>
+        <v>0.16</v>
       </c>
       <c r="Z14" t="s">
         <v>197</v>
       </c>
       <c r="AA14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AB14">
-        <v>12.1464997681966</v>
+        <v>15.7951107363978</v>
       </c>
       <c r="AC14">
-        <v>53699</v>
+        <v>60481</v>
       </c>
       <c r="AD14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>14.3</v>
+        <v>16</v>
       </c>
       <c r="AF14">
         <v>5</v>
@@ -2513,94 +2513,94 @@
         <v>45</v>
       </c>
       <c r="B15">
-        <v>17798</v>
+        <v>15337</v>
       </c>
       <c r="C15">
-        <v>8147</v>
+        <v>6621</v>
       </c>
       <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>75</v>
+      </c>
+      <c r="N15">
+        <v>50</v>
+      </c>
+      <c r="O15">
+        <v>50</v>
+      </c>
+      <c r="P15">
+        <v>2.5</v>
+      </c>
+      <c r="Q15">
+        <v>8</v>
+      </c>
+      <c r="R15" t="s">
+        <v>108</v>
+      </c>
+      <c r="S15">
+        <v>3834</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15">
         <v>5</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>4</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>20</v>
-      </c>
-      <c r="O15">
-        <v>80</v>
-      </c>
-      <c r="P15">
-        <v>4</v>
-      </c>
-      <c r="Q15">
-        <v>11</v>
-      </c>
-      <c r="R15" t="s">
-        <v>109</v>
-      </c>
-      <c r="S15">
-        <v>3560</v>
-      </c>
-      <c r="T15">
-        <v>20</v>
-      </c>
-      <c r="U15" t="b">
-        <v>0</v>
-      </c>
-      <c r="V15" t="b">
-        <v>1</v>
-      </c>
-      <c r="W15">
-        <v>4</v>
       </c>
       <c r="X15" t="s">
         <v>124</v>
       </c>
       <c r="Y15">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="Z15" t="s">
         <v>198</v>
       </c>
       <c r="AA15" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AB15">
-        <v>35.09875408544925</v>
+        <v>26.65128595503306</v>
       </c>
       <c r="AC15">
-        <v>33653.73333333333</v>
+        <v>42852.77777777778</v>
       </c>
       <c r="AD15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE15">
-        <v>23.7</v>
+        <v>19.5</v>
       </c>
       <c r="AF15">
         <v>5</v>
@@ -2611,61 +2611,61 @@
         <v>46</v>
       </c>
       <c r="B16">
-        <v>3033</v>
+        <v>17798</v>
       </c>
       <c r="C16">
-        <v>1394</v>
+        <v>8147</v>
       </c>
       <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
         <v>4</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>3</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="O16">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S16">
-        <v>758</v>
+        <v>3560</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -2674,13 +2674,13 @@
         <v>1</v>
       </c>
       <c r="W16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X16" t="s">
         <v>125</v>
       </c>
       <c r="Y16">
-        <v>0.216</v>
+        <v>0.237</v>
       </c>
       <c r="Z16" t="s">
         <v>199</v>
@@ -2689,19 +2689,19 @@
         <v>268</v>
       </c>
       <c r="AB16">
-        <v>39.47179649750809</v>
+        <v>35.09875408544925</v>
       </c>
       <c r="AC16">
-        <v>33457</v>
+        <v>33653.73333333333</v>
       </c>
       <c r="AD16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE16">
-        <v>21.6</v>
+        <v>23.7</v>
       </c>
       <c r="AF16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -2709,13 +2709,13 @@
         <v>47</v>
       </c>
       <c r="B17">
-        <v>1091</v>
+        <v>3033</v>
       </c>
       <c r="C17">
-        <v>473</v>
+        <v>1394</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2739,28 +2739,28 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="O17">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="P17">
-        <v>1.333333333333333</v>
+        <v>3.75</v>
       </c>
       <c r="Q17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S17">
-        <v>364</v>
+        <v>758</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>126</v>
       </c>
       <c r="Y17">
-        <v>0.202</v>
+        <v>0.216</v>
       </c>
       <c r="Z17" t="s">
         <v>200</v>
@@ -2787,16 +2787,16 @@
         <v>269</v>
       </c>
       <c r="AB17">
-        <v>27.229997055395</v>
+        <v>39.47179649750809</v>
       </c>
       <c r="AC17">
-        <v>43331</v>
+        <v>33457</v>
       </c>
       <c r="AD17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17">
-        <v>20.2</v>
+        <v>21.6</v>
       </c>
       <c r="AF17">
         <v>4</v>
@@ -2807,67 +2807,67 @@
         <v>48</v>
       </c>
       <c r="B18">
-        <v>259720</v>
+        <v>1091</v>
       </c>
       <c r="C18">
-        <v>119271</v>
+        <v>473</v>
       </c>
       <c r="D18">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>87.2</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>57</v>
+        <v>33.3</v>
       </c>
       <c r="O18">
-        <v>62.8</v>
+        <v>33.3</v>
       </c>
       <c r="P18">
-        <v>2.197674418604651</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Q18">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S18">
-        <v>3020</v>
+        <v>364</v>
       </c>
       <c r="T18">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18">
         <v>3</v>
@@ -2876,7 +2876,7 @@
         <v>127</v>
       </c>
       <c r="Y18">
-        <v>0.14</v>
+        <v>0.202</v>
       </c>
       <c r="Z18" t="s">
         <v>201</v>
@@ -2885,19 +2885,19 @@
         <v>270</v>
       </c>
       <c r="AB18">
-        <v>17.26007516464241</v>
+        <v>27.229997055395</v>
       </c>
       <c r="AC18">
-        <v>68590.43093922651</v>
+        <v>43331</v>
       </c>
       <c r="AD18">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="AE18">
-        <v>14</v>
+        <v>20.2</v>
       </c>
       <c r="AF18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -2905,67 +2905,67 @@
         <v>49</v>
       </c>
       <c r="B19">
-        <v>281</v>
+        <v>259720</v>
       </c>
       <c r="C19">
-        <v>132</v>
+        <v>119271</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>87.2</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>62.8</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>2.197674418604651</v>
       </c>
       <c r="Q19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S19">
-        <v>281</v>
+        <v>3020</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19">
         <v>3</v>
@@ -2974,25 +2974,25 @@
         <v>128</v>
       </c>
       <c r="Y19">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="s">
         <v>202</v>
       </c>
       <c r="AA19" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="AB19">
-        <v>8.32682799895915</v>
+        <v>17.26007516464241</v>
       </c>
       <c r="AC19">
-        <v>63849</v>
+        <v>68590.43093922651</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AE19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AF19">
         <v>3</v>
@@ -3078,7 +3078,7 @@
         <v>203</v>
       </c>
       <c r="AA20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AB20">
         <v>15.55547228644085</v>
@@ -3274,7 +3274,7 @@
         <v>205</v>
       </c>
       <c r="AA22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB22">
         <v>11.48220438684129</v>
@@ -3303,7 +3303,7 @@
         <v>33</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -3336,10 +3336,10 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -3348,7 +3348,7 @@
         <v>106</v>
       </c>
       <c r="S23">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>206</v>
       </c>
       <c r="AA23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AB23">
         <v>3.53581142339075</v>
@@ -3470,7 +3470,7 @@
         <v>207</v>
       </c>
       <c r="AA24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AB24">
         <v>33.55941432703644</v>
@@ -3493,22 +3493,22 @@
         <v>55</v>
       </c>
       <c r="B25">
-        <v>248</v>
+        <v>3260</v>
       </c>
       <c r="C25">
-        <v>122</v>
+        <v>1555</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3520,34 +3520,34 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <v>2</v>
       </c>
       <c r="M25">
-        <v>66.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="N25">
-        <v>66.7</v>
+        <v>58.8</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>47.1</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="Q25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S25">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -3562,25 +3562,25 @@
         <v>134</v>
       </c>
       <c r="Y25">
-        <v>0.114</v>
+        <v>0.115</v>
       </c>
       <c r="Z25" t="s">
         <v>208</v>
       </c>
       <c r="AA25" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AB25">
-        <v>20.7642596234897</v>
+        <v>10.56717274351188</v>
       </c>
       <c r="AC25">
-        <v>68450</v>
+        <v>71494.25</v>
       </c>
       <c r="AD25">
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AF25">
         <v>3</v>
@@ -3591,13 +3591,13 @@
         <v>56</v>
       </c>
       <c r="B26">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C26">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -3642,7 +3642,7 @@
         <v>106</v>
       </c>
       <c r="S26">
-        <v>249</v>
+        <v>124</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -3660,25 +3660,25 @@
         <v>135</v>
       </c>
       <c r="Y26">
-        <v>0.135</v>
+        <v>0.114</v>
       </c>
       <c r="Z26" t="s">
         <v>209</v>
       </c>
       <c r="AA26" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="AB26">
-        <v>7.268578878748371</v>
+        <v>20.7642596234897</v>
       </c>
       <c r="AC26">
-        <v>57875</v>
+        <v>68450</v>
       </c>
       <c r="AD26">
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>13.5</v>
+        <v>11.4</v>
       </c>
       <c r="AF26">
         <v>3</v>
@@ -3689,61 +3689,61 @@
         <v>57</v>
       </c>
       <c r="B27">
-        <v>3260</v>
+        <v>281</v>
       </c>
       <c r="C27">
-        <v>1555</v>
+        <v>132</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>100</v>
+      </c>
+      <c r="P27">
         <v>4</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>2</v>
-      </c>
-      <c r="L27">
-        <v>2</v>
-      </c>
-      <c r="M27">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="N27">
-        <v>58.8</v>
-      </c>
-      <c r="O27">
-        <v>47.1</v>
-      </c>
-      <c r="P27">
-        <v>1.235294117647059</v>
-      </c>
       <c r="Q27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S27">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="T27">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -3758,25 +3758,25 @@
         <v>136</v>
       </c>
       <c r="Y27">
-        <v>0.115</v>
+        <v>0.135</v>
       </c>
       <c r="Z27" t="s">
         <v>210</v>
       </c>
       <c r="AA27" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="AB27">
-        <v>10.56717274351188</v>
+        <v>8.32682799895915</v>
       </c>
       <c r="AC27">
-        <v>71494.25</v>
+        <v>63849</v>
       </c>
       <c r="AD27">
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF27">
         <v>3</v>
@@ -3862,7 +3862,7 @@
         <v>211</v>
       </c>
       <c r="AA28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AB28">
         <v>10.98200315956885</v>
@@ -3960,7 +3960,7 @@
         <v>189</v>
       </c>
       <c r="AA29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB29">
         <v>9.88428158148505</v>
@@ -4058,7 +4058,7 @@
         <v>212</v>
       </c>
       <c r="AA30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AB30">
         <v>16.6188482216708</v>
@@ -4156,7 +4156,7 @@
         <v>213</v>
       </c>
       <c r="AA31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AB31">
         <v>22.9785145516815</v>
@@ -4254,7 +4254,7 @@
         <v>214</v>
       </c>
       <c r="AA32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AB32">
         <v>14.8293963254593</v>
@@ -4352,7 +4352,7 @@
         <v>215</v>
       </c>
       <c r="AA33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AB33">
         <v>20.36663306550204</v>
@@ -4447,10 +4447,10 @@
         <v>0.116</v>
       </c>
       <c r="Z34" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AA34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AB34">
         <v>14.11904489235</v>
@@ -4646,7 +4646,7 @@
         <v>217</v>
       </c>
       <c r="AA36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AB36">
         <v>17.1103809315335</v>
@@ -4744,7 +4744,7 @@
         <v>218</v>
       </c>
       <c r="AA37" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AB37">
         <v>15.51486597305606</v>
@@ -4842,7 +4842,7 @@
         <v>219</v>
       </c>
       <c r="AA38" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AB38">
         <v>18.620890311318</v>
@@ -4940,7 +4940,7 @@
         <v>220</v>
       </c>
       <c r="AA39" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AB39">
         <v>32.93807267950098</v>
@@ -4963,19 +4963,19 @@
         <v>70</v>
       </c>
       <c r="B40">
-        <v>2561</v>
+        <v>249</v>
       </c>
       <c r="C40">
-        <v>1271</v>
+        <v>115</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4999,22 +4999,22 @@
         <v>100</v>
       </c>
       <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>100</v>
       </c>
-      <c r="O40">
-        <v>50</v>
-      </c>
       <c r="P40">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="S40">
-        <v>1280</v>
+        <v>249</v>
       </c>
       <c r="T40">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40">
         <v>3</v>
@@ -5032,25 +5032,25 @@
         <v>149</v>
       </c>
       <c r="Y40">
-        <v>0.185</v>
+        <v>0.135</v>
       </c>
       <c r="Z40" t="s">
         <v>221</v>
       </c>
       <c r="AA40" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="AB40">
-        <v>24.1636296257439</v>
+        <v>7.268578878748371</v>
       </c>
       <c r="AC40">
-        <v>46913.66666666666</v>
+        <v>57875</v>
       </c>
       <c r="AD40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF40">
         <v>3</v>
@@ -5136,7 +5136,7 @@
         <v>222</v>
       </c>
       <c r="AA41" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AB41">
         <v>17.91530339429697</v>
@@ -5234,7 +5234,7 @@
         <v>223</v>
       </c>
       <c r="AA42" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AB42">
         <v>37.48260738597017</v>
@@ -5528,7 +5528,7 @@
         <v>226</v>
       </c>
       <c r="AA45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AB45">
         <v>13.76209990809102</v>
@@ -5724,7 +5724,7 @@
         <v>228</v>
       </c>
       <c r="AA47" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="AB47">
         <v>18.91913348477285</v>
@@ -5822,7 +5822,7 @@
         <v>229</v>
       </c>
       <c r="AA48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB48">
         <v>11.70126280863145</v>
@@ -5949,10 +5949,10 @@
         <v>2570</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -5976,16 +5976,16 @@
         <v>2</v>
       </c>
       <c r="M50">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N50">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O50">
         <v>100</v>
       </c>
       <c r="P50">
-        <v>2.5</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="Q50">
         <v>8</v>
@@ -5994,10 +5994,10 @@
         <v>108</v>
       </c>
       <c r="S50">
-        <v>723</v>
+        <v>826</v>
       </c>
       <c r="T50">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="U50" t="b">
         <v>0</v>
@@ -6018,7 +6018,7 @@
         <v>231</v>
       </c>
       <c r="AA50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AB50">
         <v>10.47677697204727</v>
@@ -6407,7 +6407,7 @@
         <v>0.142</v>
       </c>
       <c r="Z54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA54" t="s">
         <v>291</v>
@@ -6508,7 +6508,7 @@
         <v>235</v>
       </c>
       <c r="AA55" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB55">
         <v>18.42384950637563</v>
@@ -6606,7 +6606,7 @@
         <v>236</v>
       </c>
       <c r="AA56" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB56">
         <v>9.86925565256</v>
@@ -6704,7 +6704,7 @@
         <v>237</v>
       </c>
       <c r="AA57" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AB57">
         <v>13.21785906579786</v>
@@ -6929,7 +6929,7 @@
         <v>803</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -6953,19 +6953,19 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N60">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O60">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>8</v>
@@ -6974,7 +6974,7 @@
         <v>108</v>
       </c>
       <c r="S60">
-        <v>350</v>
+        <v>438</v>
       </c>
       <c r="T60">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>241</v>
       </c>
       <c r="AA62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB62">
         <v>20.3029065312299</v>
@@ -7684,7 +7684,7 @@
         <v>246</v>
       </c>
       <c r="AA67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AB67">
         <v>9.460431841561114</v>
@@ -7782,7 +7782,7 @@
         <v>247</v>
       </c>
       <c r="AA68" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AB68">
         <v>26.46976704214084</v>
@@ -7978,7 +7978,7 @@
         <v>249</v>
       </c>
       <c r="AA70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AB70">
         <v>9.767140251129691</v>
@@ -8076,7 +8076,7 @@
         <v>250</v>
       </c>
       <c r="AA71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AB71">
         <v>8.876398510931251</v>
@@ -8174,7 +8174,7 @@
         <v>251</v>
       </c>
       <c r="AA72" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AB72">
         <v>15.52107361214972</v>
@@ -8370,7 +8370,7 @@
         <v>253</v>
       </c>
       <c r="AA74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB74">
         <v>14.38464784497463</v>

--- a/food_access_county.xlsx
+++ b/food_access_county.xlsx
@@ -2929,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>12</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>3</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66">
         <v>2</v>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K74">
         <v>11</v>
